--- a/file/table/TSIG_Muskingum.xlsx
+++ b/file/table/TSIG_Muskingum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910A801-C2AC-4A11-AC5F-F41F9CF48954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FC560D-F81B-492D-B105-949977941517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{293BEA77-BE37-42CC-81CC-CF669E9BF0C2}"/>
   </bookViews>
@@ -18,9 +18,6 @@
     <sheet name="Calculo" sheetId="1" r:id="rId3"/>
     <sheet name="{R}" sheetId="3" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Database" localSheetId="0">#REF!</definedName>
     <definedName name="_xlnm.Database" localSheetId="1">#REF!</definedName>
@@ -59,7 +56,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Salto de tiempo de modelación en HEC-HMS</t>
         </r>
@@ -205,33 +202,33 @@
     <t>Teniendo en cuenta la información topográfica e hidrológica recolectada y luego de correr el programa con diferentes valores de los parámetros obtenidos para la cuenca, se adoptaron unos criterios que se presentan a continuación. Los valores adoptados se podrán afinar posteriormente con información más detallada de diferentes parámetros físicos de la cuenca y los cauces. En general y de acuerdo con la topografía de la zona de estudio, las cuencas se dividieron en 3 partes, según la cota del centroide del cauce: alta, media y baja. Los límites de esta clasificación son elevaciones entre 60 m y 300 m.</t>
   </si>
   <si>
-    <t>Tiempo de viaje K: el tiempo de viaje se estimó utilizando la ley de Seddon:</t>
+    <t>Este valor se aproxima al entero superior. Para la cuenca media, se tomó la cuarta parte de este valor, lo que corresponde a un número de Courant cr = 0.25 y que está dentro del intervalo recomendado para estabilidad numérica y garantizar que C1 ≥ 0.</t>
+  </si>
+  <si>
+    <t>n eval</t>
+  </si>
+  <si>
+    <t>Estimación de parámetros Muskingum para la cuenca en estudio</t>
+  </si>
+  <si>
+    <t>Celeridad, c (m/s)</t>
+  </si>
+  <si>
+    <t>K (hr)</t>
+  </si>
+  <si>
+    <t>Elevación (m.s.n.m)</t>
+  </si>
+  <si>
+    <t>&lt;&lt;&lt;</t>
+  </si>
+  <si>
+    <t>1. Tiempo de viaje K: el tiempo de viaje se estimó utilizando la ley de Seddon:</t>
   </si>
   <si>
     <t>Los datos de la longitud del cauce (L) se tomaron directamente del modelo geográfico desarrollado en GEO-HMS. Teniendo en cuenta las dificultades en el cálculo de las pendientes y en la determinación de la extensión en las planicies, se establecieron, con base en las pendientes medias de cada sector las siguientes velocidades de la onda de propagación: en la cuenca alta c=2 m/s, en la media c=0.6m/s y en la baja c=0.25m/s. Para estas estimaciones también se tuvieron en cuenta los tiempos observados entre los picos de los hidrogramas medidos y las observaciones cualitativas disponibles. 
-Factor de ponderación X: Este parámetro oscila entre X=0 para el embalse lineal, donde el mecanismo principal es el de almacenamiento, y por tanto una mayor atenuación de la creciente y X=0.5 para ondas puramente cinemáticas, donde no hay atenuación del hidrograma sino puramente translación. Teniendo en cuenta, que en la cuenca baja las pendientes son muy suaves y se presentan desbordamientos y flujos laterales en las planicies, se tomó X=0. Siguiendo recomendaciones generales, para cauces naturales, en la cuenca alta se fijó X=0.2 y un valor intermedio en la cuenca media, con X=0.1.
-Número de subtramos nx: El número de subtramos tiene una gran incidencia en la atenuación de los hidrogramas. A mayor número de subtramos, menor es la atenuación. Se puede demostrar que es proporcional al número de Courant cr. Para números de Courant menores que 1, las ecuaciones de la onda cinemática presentan atenuación numérica. En las mediciones hidrológicas disponibles, se puede apreciar una fuerte atenuación de los hidrogramas en la cuenca baja. Por consiguiente, la modelación en la parte baja debe reflejarlo y esto se logra con el menor número de pasos. Consecuentemente con lo anteriormente explicado y para obtener atenuaciones numéricas, en la cuenca baja se tomaron 2 subtramos, que corresponde a un número de Courant bajo. En la cuenca alta se calculó el número de tramos correspondiente al límite superior de las recomendaciones para el cr = 1:</t>
-  </si>
-  <si>
-    <t>Este valor se aproxima al entero superior. Para la cuenca media, se tomó la cuarta parte de este valor, lo que corresponde a un número de Courant cr = 0.25 y que está dentro del intervalo recomendado para estabilidad numérica y garantizar que C1 ≥ 0.</t>
-  </si>
-  <si>
-    <t>n eval</t>
-  </si>
-  <si>
-    <t>Estimación de parámetros Muskingum para la cuenca en estudio</t>
-  </si>
-  <si>
-    <t>Celeridad, c (m/s)</t>
-  </si>
-  <si>
-    <t>K (hr)</t>
-  </si>
-  <si>
-    <t>Elevación (m.s.n.m)</t>
-  </si>
-  <si>
-    <t>&lt;&lt;&lt;</t>
+2. Factor de ponderación X: Este parámetro oscila entre X=0 para el embalse lineal, donde el mecanismo principal es el de almacenamiento, y por tanto una mayor atenuación de la creciente y X=0.5 para ondas puramente cinemáticas, donde no hay atenuación del hidrograma sino puramente translación. Teniendo en cuenta, que en la cuenca baja las pendientes son muy suaves y se presentan desbordamientos y flujos laterales en las planicies, se tomó X=0. Siguiendo recomendaciones generales, para cauces naturales, en la cuenca alta se fijó X=0.2 y un valor intermedio en la cuenca media, con X=0.1.
+3. Número de subtramos nx: El número de subtramos tiene una gran incidencia en la atenuación de los hidrogramas. A mayor número de subtramos, menor es la atenuación. Se puede demostrar que es proporcional al número de Courant cr. Para números de Courant menores que 1, las ecuaciones de la onda cinemática presentan atenuación numérica. En las mediciones hidrológicas disponibles, se puede apreciar una fuerte atenuación de los hidrogramas en la cuenca baja. Por consiguiente, la modelación en la parte baja debe reflejarlo y esto se logra con el menor número de pasos. Consecuentemente con lo anteriormente explicado y para obtener atenuaciones numéricas, en la cuenca baja se tomaron 2 subtramos, que corresponde a un número de Courant bajo. En la cuenca alta se calculó el número de tramos correspondiente al límite superior de las recomendaciones para el cr = 1:</t>
   </si>
 </sst>
 </file>
@@ -294,7 +291,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -490,7 +487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -531,9 +528,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -586,15 +580,15 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1194,35 +1188,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="FCD"/>
-      <sheetName val="5.1.5.9.1.4.4"/>
-      <sheetName val="5.1.5.9.1.4.5 Texto"/>
-      <sheetName val="5.1.5.9.1.4.5_2019"/>
-      <sheetName val="5.1.5.9.1.4.5_2024"/>
-      <sheetName val="5.1.5.9.1.4.5_2029"/>
-      <sheetName val="5.1.5.9.1.4.6"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -1523,850 +1488,850 @@
   <dimension ref="B2:B274"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="4.1328125" style="33" customWidth="1"/>
-    <col min="2" max="2" width="107.46484375" style="32" customWidth="1"/>
-    <col min="3" max="16384" width="9.1328125" style="33"/>
+    <col min="1" max="1" width="4.1328125" style="31" customWidth="1"/>
+    <col min="2" max="2" width="107.46484375" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="31"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B5" s="33"/>
+      <c r="B5" s="31"/>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="32" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="47.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="33"/>
+      <c r="B7" s="31"/>
     </row>
     <row r="8" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="48" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="33"/>
+      <c r="B9" s="31"/>
     </row>
     <row r="10" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="32" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="159" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B11" s="34"/>
+      <c r="B11" s="32"/>
     </row>
     <row r="12" spans="2:2" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B13" s="34"/>
+      <c r="B13" s="32"/>
     </row>
     <row r="14" spans="2:2" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="39" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B16" s="34"/>
+      <c r="B16" s="32"/>
     </row>
     <row r="17" spans="2:2" ht="82.5" x14ac:dyDescent="0.6">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="138.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B18" s="34"/>
+      <c r="B18" s="32"/>
     </row>
     <row r="19" spans="2:2" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="32" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="32" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B21" s="34"/>
+      <c r="B21" s="32"/>
     </row>
     <row r="22" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="32" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B23" s="34"/>
+      <c r="B23" s="32"/>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B24" s="34"/>
+      <c r="B24" s="32"/>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B25" s="34"/>
+      <c r="B25" s="32"/>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B26" s="34"/>
+      <c r="B26" s="32"/>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B27" s="34"/>
+      <c r="B27" s="32"/>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B28" s="34"/>
+      <c r="B28" s="32"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B29" s="34"/>
+      <c r="B29" s="32"/>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B30" s="34"/>
+      <c r="B30" s="32"/>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B31" s="34"/>
+      <c r="B31" s="32"/>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B32" s="34"/>
+      <c r="B32" s="32"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B33" s="34"/>
+      <c r="B33" s="32"/>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B34" s="34"/>
+      <c r="B34" s="32"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B35" s="34"/>
+      <c r="B35" s="32"/>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B36" s="34"/>
+      <c r="B36" s="32"/>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B37" s="34"/>
+      <c r="B37" s="32"/>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B38" s="34"/>
+      <c r="B38" s="32"/>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B39" s="34"/>
+      <c r="B39" s="32"/>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B40" s="34"/>
+      <c r="B40" s="32"/>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B41" s="34"/>
+      <c r="B41" s="32"/>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B42" s="34"/>
+      <c r="B42" s="32"/>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B43" s="34"/>
+      <c r="B43" s="32"/>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B44" s="34"/>
+      <c r="B44" s="32"/>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B45" s="34"/>
+      <c r="B45" s="32"/>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B46" s="34"/>
+      <c r="B46" s="32"/>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B47" s="34"/>
+      <c r="B47" s="32"/>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B48" s="34"/>
+      <c r="B48" s="32"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B49" s="34"/>
+      <c r="B49" s="32"/>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B50" s="34"/>
+      <c r="B50" s="32"/>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B51" s="34"/>
+      <c r="B51" s="32"/>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B52" s="34"/>
+      <c r="B52" s="32"/>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B53" s="34"/>
+      <c r="B53" s="32"/>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B54" s="34"/>
+      <c r="B54" s="32"/>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B55" s="34"/>
+      <c r="B55" s="32"/>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B56" s="34"/>
+      <c r="B56" s="32"/>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B57" s="34"/>
+      <c r="B57" s="32"/>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B58" s="34"/>
+      <c r="B58" s="32"/>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B59" s="34"/>
+      <c r="B59" s="32"/>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B60" s="34"/>
+      <c r="B60" s="32"/>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B61" s="34"/>
+      <c r="B61" s="32"/>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B62" s="34"/>
+      <c r="B62" s="32"/>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B63" s="34"/>
+      <c r="B63" s="32"/>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B64" s="34"/>
+      <c r="B64" s="32"/>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B65" s="34"/>
+      <c r="B65" s="32"/>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B66" s="34"/>
+      <c r="B66" s="32"/>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B67" s="34"/>
+      <c r="B67" s="32"/>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B68" s="34"/>
+      <c r="B68" s="32"/>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B69" s="34"/>
+      <c r="B69" s="32"/>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B70" s="34"/>
+      <c r="B70" s="32"/>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B71" s="34"/>
+      <c r="B71" s="32"/>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B72" s="34"/>
+      <c r="B72" s="32"/>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B73" s="34"/>
+      <c r="B73" s="32"/>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B74" s="34"/>
+      <c r="B74" s="32"/>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B75" s="34"/>
+      <c r="B75" s="32"/>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B76" s="34"/>
+      <c r="B76" s="32"/>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B77" s="34"/>
+      <c r="B77" s="32"/>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B78" s="34"/>
+      <c r="B78" s="32"/>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B79" s="34"/>
+      <c r="B79" s="32"/>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B80" s="34"/>
+      <c r="B80" s="32"/>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B81" s="34"/>
+      <c r="B81" s="32"/>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B82" s="34"/>
+      <c r="B82" s="32"/>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B83" s="34"/>
+      <c r="B83" s="32"/>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B84" s="34"/>
+      <c r="B84" s="32"/>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B85" s="34"/>
+      <c r="B85" s="32"/>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B86" s="34"/>
+      <c r="B86" s="32"/>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B87" s="34"/>
+      <c r="B87" s="32"/>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B88" s="34"/>
+      <c r="B88" s="32"/>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B89" s="34"/>
+      <c r="B89" s="32"/>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B90" s="34"/>
+      <c r="B90" s="32"/>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B91" s="34"/>
+      <c r="B91" s="32"/>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B92" s="34"/>
+      <c r="B92" s="32"/>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B93" s="34"/>
+      <c r="B93" s="32"/>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B94" s="34"/>
+      <c r="B94" s="32"/>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B95" s="34"/>
+      <c r="B95" s="32"/>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B96" s="34"/>
+      <c r="B96" s="32"/>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B97" s="34"/>
+      <c r="B97" s="32"/>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B98" s="34"/>
+      <c r="B98" s="32"/>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B99" s="34"/>
+      <c r="B99" s="32"/>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B100" s="34"/>
+      <c r="B100" s="32"/>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B101" s="34"/>
+      <c r="B101" s="32"/>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B102" s="34"/>
+      <c r="B102" s="32"/>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B103" s="34"/>
+      <c r="B103" s="32"/>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B104" s="34"/>
+      <c r="B104" s="32"/>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B105" s="34"/>
+      <c r="B105" s="32"/>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B106" s="34"/>
+      <c r="B106" s="32"/>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B107" s="34"/>
+      <c r="B107" s="32"/>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B108" s="34"/>
+      <c r="B108" s="32"/>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B109" s="34"/>
+      <c r="B109" s="32"/>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B110" s="34"/>
+      <c r="B110" s="32"/>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B111" s="34"/>
+      <c r="B111" s="32"/>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B112" s="34"/>
+      <c r="B112" s="32"/>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B113" s="34"/>
+      <c r="B113" s="32"/>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B114" s="34"/>
+      <c r="B114" s="32"/>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B115" s="34"/>
+      <c r="B115" s="32"/>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B116" s="34"/>
+      <c r="B116" s="32"/>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B117" s="34"/>
+      <c r="B117" s="32"/>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B118" s="34"/>
+      <c r="B118" s="32"/>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B119" s="34"/>
+      <c r="B119" s="32"/>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B120" s="34"/>
+      <c r="B120" s="32"/>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B121" s="34"/>
+      <c r="B121" s="32"/>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B122" s="34"/>
+      <c r="B122" s="32"/>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B123" s="34"/>
+      <c r="B123" s="32"/>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B124" s="34"/>
+      <c r="B124" s="32"/>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B125" s="34"/>
+      <c r="B125" s="32"/>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B126" s="34"/>
+      <c r="B126" s="32"/>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B127" s="34"/>
+      <c r="B127" s="32"/>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B128" s="34"/>
+      <c r="B128" s="32"/>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B129" s="34"/>
+      <c r="B129" s="32"/>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B130" s="34"/>
+      <c r="B130" s="32"/>
     </row>
     <row r="131" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B131" s="34"/>
+      <c r="B131" s="32"/>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B132" s="34"/>
+      <c r="B132" s="32"/>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B133" s="34"/>
+      <c r="B133" s="32"/>
     </row>
     <row r="134" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B134" s="34"/>
+      <c r="B134" s="32"/>
     </row>
     <row r="135" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B135" s="34"/>
+      <c r="B135" s="32"/>
     </row>
     <row r="136" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B136" s="34"/>
+      <c r="B136" s="32"/>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B137" s="34"/>
+      <c r="B137" s="32"/>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B138" s="34"/>
+      <c r="B138" s="32"/>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B139" s="34"/>
+      <c r="B139" s="32"/>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B140" s="34"/>
+      <c r="B140" s="32"/>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B141" s="34"/>
+      <c r="B141" s="32"/>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B142" s="34"/>
+      <c r="B142" s="32"/>
     </row>
     <row r="143" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B143" s="34"/>
+      <c r="B143" s="32"/>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B144" s="34"/>
+      <c r="B144" s="32"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B145" s="34"/>
+      <c r="B145" s="32"/>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B146" s="34"/>
+      <c r="B146" s="32"/>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B147" s="34"/>
+      <c r="B147" s="32"/>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B148" s="34"/>
+      <c r="B148" s="32"/>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B149" s="34"/>
+      <c r="B149" s="32"/>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B150" s="34"/>
+      <c r="B150" s="32"/>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B151" s="34"/>
+      <c r="B151" s="32"/>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B152" s="34"/>
+      <c r="B152" s="32"/>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B153" s="34"/>
+      <c r="B153" s="32"/>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B154" s="34"/>
+      <c r="B154" s="32"/>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B155" s="34"/>
+      <c r="B155" s="32"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B156" s="34"/>
+      <c r="B156" s="32"/>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B157" s="34"/>
+      <c r="B157" s="32"/>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B158" s="34"/>
+      <c r="B158" s="32"/>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B159" s="34"/>
+      <c r="B159" s="32"/>
     </row>
     <row r="160" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B160" s="34"/>
+      <c r="B160" s="32"/>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B161" s="34"/>
+      <c r="B161" s="32"/>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B162" s="34"/>
+      <c r="B162" s="32"/>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B163" s="34"/>
+      <c r="B163" s="32"/>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B164" s="34"/>
+      <c r="B164" s="32"/>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B165" s="34"/>
+      <c r="B165" s="32"/>
     </row>
     <row r="166" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B166" s="34"/>
+      <c r="B166" s="32"/>
     </row>
     <row r="167" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B167" s="34"/>
+      <c r="B167" s="32"/>
     </row>
     <row r="168" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B168" s="34"/>
+      <c r="B168" s="32"/>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B169" s="34"/>
+      <c r="B169" s="32"/>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B170" s="34"/>
+      <c r="B170" s="32"/>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B171" s="34"/>
+      <c r="B171" s="32"/>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B172" s="34"/>
+      <c r="B172" s="32"/>
     </row>
     <row r="173" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B173" s="34"/>
+      <c r="B173" s="32"/>
     </row>
     <row r="174" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B174" s="34"/>
+      <c r="B174" s="32"/>
     </row>
     <row r="175" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B175" s="34"/>
+      <c r="B175" s="32"/>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B176" s="34"/>
+      <c r="B176" s="32"/>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B177" s="34"/>
+      <c r="B177" s="32"/>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B178" s="34"/>
+      <c r="B178" s="32"/>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B179" s="34"/>
+      <c r="B179" s="32"/>
     </row>
     <row r="180" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B180" s="34"/>
+      <c r="B180" s="32"/>
     </row>
     <row r="181" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B181" s="34"/>
+      <c r="B181" s="32"/>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B182" s="34"/>
+      <c r="B182" s="32"/>
     </row>
     <row r="183" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B183" s="34"/>
+      <c r="B183" s="32"/>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B184" s="34"/>
+      <c r="B184" s="32"/>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B185" s="34"/>
+      <c r="B185" s="32"/>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B186" s="34"/>
+      <c r="B186" s="32"/>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B187" s="34"/>
+      <c r="B187" s="32"/>
     </row>
     <row r="188" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B188" s="34"/>
+      <c r="B188" s="32"/>
     </row>
     <row r="189" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B189" s="34"/>
+      <c r="B189" s="32"/>
     </row>
     <row r="190" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B190" s="34"/>
+      <c r="B190" s="32"/>
     </row>
     <row r="191" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B191" s="34"/>
+      <c r="B191" s="32"/>
     </row>
     <row r="192" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B192" s="34"/>
+      <c r="B192" s="32"/>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B193" s="34"/>
+      <c r="B193" s="32"/>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B194" s="34"/>
+      <c r="B194" s="32"/>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B195" s="34"/>
+      <c r="B195" s="32"/>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B196" s="34"/>
+      <c r="B196" s="32"/>
     </row>
     <row r="197" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B197" s="34"/>
+      <c r="B197" s="32"/>
     </row>
     <row r="198" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B198" s="34"/>
+      <c r="B198" s="32"/>
     </row>
     <row r="199" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B199" s="34"/>
+      <c r="B199" s="32"/>
     </row>
     <row r="200" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B200" s="34"/>
+      <c r="B200" s="32"/>
     </row>
     <row r="201" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B201" s="34"/>
+      <c r="B201" s="32"/>
     </row>
     <row r="202" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B202" s="34"/>
+      <c r="B202" s="32"/>
     </row>
     <row r="203" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B203" s="34"/>
+      <c r="B203" s="32"/>
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B204" s="34"/>
+      <c r="B204" s="32"/>
     </row>
     <row r="205" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B205" s="34"/>
+      <c r="B205" s="32"/>
     </row>
     <row r="206" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B206" s="34"/>
+      <c r="B206" s="32"/>
     </row>
     <row r="207" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B207" s="34"/>
+      <c r="B207" s="32"/>
     </row>
     <row r="208" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B208" s="34"/>
+      <c r="B208" s="32"/>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B209" s="34"/>
+      <c r="B209" s="32"/>
     </row>
     <row r="210" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B210" s="34"/>
+      <c r="B210" s="32"/>
     </row>
     <row r="211" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B211" s="34"/>
+      <c r="B211" s="32"/>
     </row>
     <row r="212" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B212" s="34"/>
+      <c r="B212" s="32"/>
     </row>
     <row r="213" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B213" s="34"/>
+      <c r="B213" s="32"/>
     </row>
     <row r="214" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B214" s="34"/>
+      <c r="B214" s="32"/>
     </row>
     <row r="215" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B215" s="34"/>
+      <c r="B215" s="32"/>
     </row>
     <row r="216" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B216" s="34"/>
+      <c r="B216" s="32"/>
     </row>
     <row r="217" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B217" s="34"/>
+      <c r="B217" s="32"/>
     </row>
     <row r="218" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B218" s="34"/>
+      <c r="B218" s="32"/>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B219" s="34"/>
+      <c r="B219" s="32"/>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B220" s="34"/>
+      <c r="B220" s="32"/>
     </row>
     <row r="221" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B221" s="34"/>
+      <c r="B221" s="32"/>
     </row>
     <row r="222" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B222" s="34"/>
+      <c r="B222" s="32"/>
     </row>
     <row r="223" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B223" s="34"/>
+      <c r="B223" s="32"/>
     </row>
     <row r="224" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B224" s="34"/>
+      <c r="B224" s="32"/>
     </row>
     <row r="225" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B225" s="34"/>
+      <c r="B225" s="32"/>
     </row>
     <row r="226" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B226" s="34"/>
+      <c r="B226" s="32"/>
     </row>
     <row r="227" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B227" s="34"/>
+      <c r="B227" s="32"/>
     </row>
     <row r="228" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B228" s="34"/>
+      <c r="B228" s="32"/>
     </row>
     <row r="229" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B229" s="34"/>
+      <c r="B229" s="32"/>
     </row>
     <row r="230" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B230" s="34"/>
+      <c r="B230" s="32"/>
     </row>
     <row r="231" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B231" s="34"/>
+      <c r="B231" s="32"/>
     </row>
     <row r="232" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B232" s="34"/>
+      <c r="B232" s="32"/>
     </row>
     <row r="233" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B233" s="34"/>
+      <c r="B233" s="32"/>
     </row>
     <row r="234" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B234" s="34"/>
+      <c r="B234" s="32"/>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B235" s="34"/>
+      <c r="B235" s="32"/>
     </row>
     <row r="236" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B236" s="34"/>
+      <c r="B236" s="32"/>
     </row>
     <row r="237" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B237" s="34"/>
+      <c r="B237" s="32"/>
     </row>
     <row r="238" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B238" s="34"/>
+      <c r="B238" s="32"/>
     </row>
     <row r="239" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B239" s="34"/>
+      <c r="B239" s="32"/>
     </row>
     <row r="240" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B240" s="34"/>
+      <c r="B240" s="32"/>
     </row>
     <row r="241" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B241" s="34"/>
+      <c r="B241" s="32"/>
     </row>
     <row r="242" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B242" s="34"/>
+      <c r="B242" s="32"/>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B243" s="34"/>
+      <c r="B243" s="32"/>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B244" s="34"/>
+      <c r="B244" s="32"/>
     </row>
     <row r="245" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B245" s="34"/>
+      <c r="B245" s="32"/>
     </row>
     <row r="246" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B246" s="34"/>
+      <c r="B246" s="32"/>
     </row>
     <row r="247" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B247" s="34"/>
+      <c r="B247" s="32"/>
     </row>
     <row r="248" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B248" s="34"/>
+      <c r="B248" s="32"/>
     </row>
     <row r="249" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B249" s="34"/>
+      <c r="B249" s="32"/>
     </row>
     <row r="250" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B250" s="34"/>
+      <c r="B250" s="32"/>
     </row>
     <row r="251" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B251" s="34"/>
+      <c r="B251" s="32"/>
     </row>
     <row r="252" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B252" s="34"/>
+      <c r="B252" s="32"/>
     </row>
     <row r="253" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B253" s="34"/>
+      <c r="B253" s="32"/>
     </row>
     <row r="254" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B254" s="34"/>
+      <c r="B254" s="32"/>
     </row>
     <row r="255" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B255" s="34"/>
+      <c r="B255" s="32"/>
     </row>
     <row r="256" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B256" s="34"/>
+      <c r="B256" s="32"/>
     </row>
     <row r="257" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B257" s="34"/>
+      <c r="B257" s="32"/>
     </row>
     <row r="258" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B258" s="34"/>
+      <c r="B258" s="32"/>
     </row>
     <row r="259" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B259" s="34"/>
+      <c r="B259" s="32"/>
     </row>
     <row r="260" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B260" s="34"/>
+      <c r="B260" s="32"/>
     </row>
     <row r="261" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B261" s="34"/>
+      <c r="B261" s="32"/>
     </row>
     <row r="262" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B262" s="34"/>
+      <c r="B262" s="32"/>
     </row>
     <row r="263" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B263" s="34"/>
+      <c r="B263" s="32"/>
     </row>
     <row r="264" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B264" s="34"/>
+      <c r="B264" s="32"/>
     </row>
     <row r="265" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B265" s="34"/>
+      <c r="B265" s="32"/>
     </row>
     <row r="266" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B266" s="34"/>
+      <c r="B266" s="32"/>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B267" s="34"/>
+      <c r="B267" s="32"/>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B268" s="34"/>
+      <c r="B268" s="32"/>
     </row>
     <row r="269" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B269" s="34"/>
+      <c r="B269" s="32"/>
     </row>
     <row r="270" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B270" s="34"/>
+      <c r="B270" s="32"/>
     </row>
     <row r="271" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B271" s="34"/>
+      <c r="B271" s="32"/>
     </row>
     <row r="272" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B272" s="34"/>
+      <c r="B272" s="32"/>
     </row>
     <row r="273" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B273" s="34"/>
+      <c r="B273" s="32"/>
     </row>
     <row r="274" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B274" s="34"/>
+      <c r="B274" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2380,840 +2345,840 @@
   <dimension ref="B2:B275"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="4.1328125" style="33" customWidth="1"/>
-    <col min="2" max="2" width="107.46484375" style="32" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="33" customWidth="1"/>
-    <col min="4" max="16384" width="9.1328125" style="33"/>
+    <col min="1" max="1" width="4.1328125" style="31" customWidth="1"/>
+    <col min="2" max="2" width="107.46484375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="31" customWidth="1"/>
+    <col min="4" max="16384" width="9.1328125" style="31"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B2" s="32" t="s">
-        <v>47</v>
+      <c r="B2" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="82.5" x14ac:dyDescent="0.6">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="32" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B5" s="34"/>
+      <c r="B5" s="32"/>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="32"/>
+    </row>
+    <row r="8" spans="2:2" ht="330" x14ac:dyDescent="0.6">
+      <c r="B8" s="32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B9" s="32"/>
+    </row>
+    <row r="10" spans="2:2" ht="33" x14ac:dyDescent="0.6">
+      <c r="B10" s="32" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="34"/>
-    </row>
-    <row r="8" spans="2:2" ht="330" x14ac:dyDescent="0.6">
-      <c r="B8" s="34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="34"/>
-    </row>
-    <row r="10" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B10" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B11" s="34"/>
+      <c r="B11" s="32"/>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B12" s="34"/>
+      <c r="B12" s="32"/>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B13" s="34"/>
+      <c r="B13" s="32"/>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B14" s="34"/>
+      <c r="B14" s="32"/>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B15" s="34"/>
+      <c r="B15" s="32"/>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B16" s="34"/>
+      <c r="B16" s="32"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B17" s="34"/>
+      <c r="B17" s="32"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B18" s="34"/>
+      <c r="B18" s="32"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B19" s="34"/>
+      <c r="B19" s="32"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B20" s="34"/>
+      <c r="B20" s="32"/>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B21" s="34"/>
+      <c r="B21" s="32"/>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B22" s="34"/>
+      <c r="B22" s="32"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B23" s="34"/>
+      <c r="B23" s="32"/>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B24" s="34"/>
+      <c r="B24" s="32"/>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B25" s="34"/>
+      <c r="B25" s="32"/>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B26" s="34"/>
+      <c r="B26" s="32"/>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B27" s="34"/>
+      <c r="B27" s="32"/>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B28" s="34"/>
+      <c r="B28" s="32"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B29" s="34"/>
+      <c r="B29" s="32"/>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B30" s="34"/>
+      <c r="B30" s="32"/>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B31" s="34"/>
+      <c r="B31" s="32"/>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B32" s="34"/>
+      <c r="B32" s="32"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B33" s="34"/>
+      <c r="B33" s="32"/>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B34" s="34"/>
+      <c r="B34" s="32"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B35" s="34"/>
+      <c r="B35" s="32"/>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B36" s="34"/>
+      <c r="B36" s="32"/>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B37" s="34"/>
+      <c r="B37" s="32"/>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B38" s="34"/>
+      <c r="B38" s="32"/>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B39" s="34"/>
+      <c r="B39" s="32"/>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B40" s="34"/>
+      <c r="B40" s="32"/>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B41" s="34"/>
+      <c r="B41" s="32"/>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B42" s="34"/>
+      <c r="B42" s="32"/>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B43" s="34"/>
+      <c r="B43" s="32"/>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B44" s="34"/>
+      <c r="B44" s="32"/>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B45" s="34"/>
+      <c r="B45" s="32"/>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B46" s="34"/>
+      <c r="B46" s="32"/>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B47" s="34"/>
+      <c r="B47" s="32"/>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B48" s="34"/>
+      <c r="B48" s="32"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B49" s="34"/>
+      <c r="B49" s="32"/>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B50" s="34"/>
+      <c r="B50" s="32"/>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B51" s="34"/>
+      <c r="B51" s="32"/>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B52" s="34"/>
+      <c r="B52" s="32"/>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B53" s="34"/>
+      <c r="B53" s="32"/>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B54" s="34"/>
+      <c r="B54" s="32"/>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B55" s="34"/>
+      <c r="B55" s="32"/>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B56" s="34"/>
+      <c r="B56" s="32"/>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B57" s="34"/>
+      <c r="B57" s="32"/>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B58" s="34"/>
+      <c r="B58" s="32"/>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B59" s="34"/>
+      <c r="B59" s="32"/>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B60" s="34"/>
+      <c r="B60" s="32"/>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B61" s="34"/>
+      <c r="B61" s="32"/>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B62" s="34"/>
+      <c r="B62" s="32"/>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B63" s="34"/>
+      <c r="B63" s="32"/>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B64" s="34"/>
+      <c r="B64" s="32"/>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B65" s="34"/>
+      <c r="B65" s="32"/>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B66" s="34"/>
+      <c r="B66" s="32"/>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B67" s="34"/>
+      <c r="B67" s="32"/>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B68" s="34"/>
+      <c r="B68" s="32"/>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B69" s="34"/>
+      <c r="B69" s="32"/>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B70" s="34"/>
+      <c r="B70" s="32"/>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B71" s="34"/>
+      <c r="B71" s="32"/>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B72" s="34"/>
+      <c r="B72" s="32"/>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B73" s="34"/>
+      <c r="B73" s="32"/>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B74" s="34"/>
+      <c r="B74" s="32"/>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B75" s="34"/>
+      <c r="B75" s="32"/>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B76" s="34"/>
+      <c r="B76" s="32"/>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B77" s="34"/>
+      <c r="B77" s="32"/>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B78" s="34"/>
+      <c r="B78" s="32"/>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B79" s="34"/>
+      <c r="B79" s="32"/>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B80" s="34"/>
+      <c r="B80" s="32"/>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B81" s="34"/>
+      <c r="B81" s="32"/>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B82" s="34"/>
+      <c r="B82" s="32"/>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B83" s="34"/>
+      <c r="B83" s="32"/>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B84" s="34"/>
+      <c r="B84" s="32"/>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B85" s="34"/>
+      <c r="B85" s="32"/>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B86" s="34"/>
+      <c r="B86" s="32"/>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B87" s="34"/>
+      <c r="B87" s="32"/>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B88" s="34"/>
+      <c r="B88" s="32"/>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B89" s="34"/>
+      <c r="B89" s="32"/>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B90" s="34"/>
+      <c r="B90" s="32"/>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B91" s="34"/>
+      <c r="B91" s="32"/>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B92" s="34"/>
+      <c r="B92" s="32"/>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B93" s="34"/>
+      <c r="B93" s="32"/>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B94" s="34"/>
+      <c r="B94" s="32"/>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B95" s="34"/>
+      <c r="B95" s="32"/>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B96" s="34"/>
+      <c r="B96" s="32"/>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B97" s="34"/>
+      <c r="B97" s="32"/>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B98" s="34"/>
+      <c r="B98" s="32"/>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B99" s="34"/>
+      <c r="B99" s="32"/>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B100" s="34"/>
+      <c r="B100" s="32"/>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B101" s="34"/>
+      <c r="B101" s="32"/>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B102" s="34"/>
+      <c r="B102" s="32"/>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B103" s="34"/>
+      <c r="B103" s="32"/>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B104" s="34"/>
+      <c r="B104" s="32"/>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B105" s="34"/>
+      <c r="B105" s="32"/>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B106" s="34"/>
+      <c r="B106" s="32"/>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B107" s="34"/>
+      <c r="B107" s="32"/>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B108" s="34"/>
+      <c r="B108" s="32"/>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B109" s="34"/>
+      <c r="B109" s="32"/>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B110" s="34"/>
+      <c r="B110" s="32"/>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B111" s="34"/>
+      <c r="B111" s="32"/>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B112" s="34"/>
+      <c r="B112" s="32"/>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B113" s="34"/>
+      <c r="B113" s="32"/>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B114" s="34"/>
+      <c r="B114" s="32"/>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B115" s="34"/>
+      <c r="B115" s="32"/>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B116" s="34"/>
+      <c r="B116" s="32"/>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B117" s="34"/>
+      <c r="B117" s="32"/>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B118" s="34"/>
+      <c r="B118" s="32"/>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B119" s="34"/>
+      <c r="B119" s="32"/>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B120" s="34"/>
+      <c r="B120" s="32"/>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B121" s="34"/>
+      <c r="B121" s="32"/>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B122" s="34"/>
+      <c r="B122" s="32"/>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B123" s="34"/>
+      <c r="B123" s="32"/>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B124" s="34"/>
+      <c r="B124" s="32"/>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B125" s="34"/>
+      <c r="B125" s="32"/>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B126" s="34"/>
+      <c r="B126" s="32"/>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B127" s="34"/>
+      <c r="B127" s="32"/>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B128" s="34"/>
+      <c r="B128" s="32"/>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B129" s="34"/>
+      <c r="B129" s="32"/>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B130" s="34"/>
+      <c r="B130" s="32"/>
     </row>
     <row r="131" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B131" s="34"/>
+      <c r="B131" s="32"/>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B132" s="34"/>
+      <c r="B132" s="32"/>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B133" s="34"/>
+      <c r="B133" s="32"/>
     </row>
     <row r="134" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B134" s="34"/>
+      <c r="B134" s="32"/>
     </row>
     <row r="135" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B135" s="34"/>
+      <c r="B135" s="32"/>
     </row>
     <row r="136" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B136" s="34"/>
+      <c r="B136" s="32"/>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B137" s="34"/>
+      <c r="B137" s="32"/>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B138" s="34"/>
+      <c r="B138" s="32"/>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B139" s="34"/>
+      <c r="B139" s="32"/>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B140" s="34"/>
+      <c r="B140" s="32"/>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B141" s="34"/>
+      <c r="B141" s="32"/>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B142" s="34"/>
+      <c r="B142" s="32"/>
     </row>
     <row r="143" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B143" s="34"/>
+      <c r="B143" s="32"/>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B144" s="34"/>
+      <c r="B144" s="32"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B145" s="34"/>
+      <c r="B145" s="32"/>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B146" s="34"/>
+      <c r="B146" s="32"/>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B147" s="34"/>
+      <c r="B147" s="32"/>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B148" s="34"/>
+      <c r="B148" s="32"/>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B149" s="34"/>
+      <c r="B149" s="32"/>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B150" s="34"/>
+      <c r="B150" s="32"/>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B151" s="34"/>
+      <c r="B151" s="32"/>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B152" s="34"/>
+      <c r="B152" s="32"/>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B153" s="34"/>
+      <c r="B153" s="32"/>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B154" s="34"/>
+      <c r="B154" s="32"/>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B155" s="34"/>
+      <c r="B155" s="32"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B156" s="34"/>
+      <c r="B156" s="32"/>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B157" s="34"/>
+      <c r="B157" s="32"/>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B158" s="34"/>
+      <c r="B158" s="32"/>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B159" s="34"/>
+      <c r="B159" s="32"/>
     </row>
     <row r="160" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B160" s="34"/>
+      <c r="B160" s="32"/>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B161" s="34"/>
+      <c r="B161" s="32"/>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B162" s="34"/>
+      <c r="B162" s="32"/>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B163" s="34"/>
+      <c r="B163" s="32"/>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B164" s="34"/>
+      <c r="B164" s="32"/>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B165" s="34"/>
+      <c r="B165" s="32"/>
     </row>
     <row r="166" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B166" s="34"/>
+      <c r="B166" s="32"/>
     </row>
     <row r="167" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B167" s="34"/>
+      <c r="B167" s="32"/>
     </row>
     <row r="168" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B168" s="34"/>
+      <c r="B168" s="32"/>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B169" s="34"/>
+      <c r="B169" s="32"/>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B170" s="34"/>
+      <c r="B170" s="32"/>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B171" s="34"/>
+      <c r="B171" s="32"/>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B172" s="34"/>
+      <c r="B172" s="32"/>
     </row>
     <row r="173" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B173" s="34"/>
+      <c r="B173" s="32"/>
     </row>
     <row r="174" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B174" s="34"/>
+      <c r="B174" s="32"/>
     </row>
     <row r="175" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B175" s="34"/>
+      <c r="B175" s="32"/>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B176" s="34"/>
+      <c r="B176" s="32"/>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B177" s="34"/>
+      <c r="B177" s="32"/>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B178" s="34"/>
+      <c r="B178" s="32"/>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B179" s="34"/>
+      <c r="B179" s="32"/>
     </row>
     <row r="180" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B180" s="34"/>
+      <c r="B180" s="32"/>
     </row>
     <row r="181" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B181" s="34"/>
+      <c r="B181" s="32"/>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B182" s="34"/>
+      <c r="B182" s="32"/>
     </row>
     <row r="183" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B183" s="34"/>
+      <c r="B183" s="32"/>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B184" s="34"/>
+      <c r="B184" s="32"/>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B185" s="34"/>
+      <c r="B185" s="32"/>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B186" s="34"/>
+      <c r="B186" s="32"/>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B187" s="34"/>
+      <c r="B187" s="32"/>
     </row>
     <row r="188" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B188" s="34"/>
+      <c r="B188" s="32"/>
     </row>
     <row r="189" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B189" s="34"/>
+      <c r="B189" s="32"/>
     </row>
     <row r="190" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B190" s="34"/>
+      <c r="B190" s="32"/>
     </row>
     <row r="191" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B191" s="34"/>
+      <c r="B191" s="32"/>
     </row>
     <row r="192" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B192" s="34"/>
+      <c r="B192" s="32"/>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B193" s="34"/>
+      <c r="B193" s="32"/>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B194" s="34"/>
+      <c r="B194" s="32"/>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B195" s="34"/>
+      <c r="B195" s="32"/>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B196" s="34"/>
+      <c r="B196" s="32"/>
     </row>
     <row r="197" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B197" s="34"/>
+      <c r="B197" s="32"/>
     </row>
     <row r="198" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B198" s="34"/>
+      <c r="B198" s="32"/>
     </row>
     <row r="199" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B199" s="34"/>
+      <c r="B199" s="32"/>
     </row>
     <row r="200" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B200" s="34"/>
+      <c r="B200" s="32"/>
     </row>
     <row r="201" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B201" s="34"/>
+      <c r="B201" s="32"/>
     </row>
     <row r="202" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B202" s="34"/>
+      <c r="B202" s="32"/>
     </row>
     <row r="203" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B203" s="34"/>
+      <c r="B203" s="32"/>
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B204" s="34"/>
+      <c r="B204" s="32"/>
     </row>
     <row r="205" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B205" s="34"/>
+      <c r="B205" s="32"/>
     </row>
     <row r="206" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B206" s="34"/>
+      <c r="B206" s="32"/>
     </row>
     <row r="207" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B207" s="34"/>
+      <c r="B207" s="32"/>
     </row>
     <row r="208" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B208" s="34"/>
+      <c r="B208" s="32"/>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B209" s="34"/>
+      <c r="B209" s="32"/>
     </row>
     <row r="210" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B210" s="34"/>
+      <c r="B210" s="32"/>
     </row>
     <row r="211" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B211" s="34"/>
+      <c r="B211" s="32"/>
     </row>
     <row r="212" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B212" s="34"/>
+      <c r="B212" s="32"/>
     </row>
     <row r="213" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B213" s="34"/>
+      <c r="B213" s="32"/>
     </row>
     <row r="214" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B214" s="34"/>
+      <c r="B214" s="32"/>
     </row>
     <row r="215" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B215" s="34"/>
+      <c r="B215" s="32"/>
     </row>
     <row r="216" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B216" s="34"/>
+      <c r="B216" s="32"/>
     </row>
     <row r="217" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B217" s="34"/>
+      <c r="B217" s="32"/>
     </row>
     <row r="218" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B218" s="34"/>
+      <c r="B218" s="32"/>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B219" s="34"/>
+      <c r="B219" s="32"/>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B220" s="34"/>
+      <c r="B220" s="32"/>
     </row>
     <row r="221" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B221" s="34"/>
+      <c r="B221" s="32"/>
     </row>
     <row r="222" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B222" s="34"/>
+      <c r="B222" s="32"/>
     </row>
     <row r="223" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B223" s="34"/>
+      <c r="B223" s="32"/>
     </row>
     <row r="224" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B224" s="34"/>
+      <c r="B224" s="32"/>
     </row>
     <row r="225" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B225" s="34"/>
+      <c r="B225" s="32"/>
     </row>
     <row r="226" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B226" s="34"/>
+      <c r="B226" s="32"/>
     </row>
     <row r="227" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B227" s="34"/>
+      <c r="B227" s="32"/>
     </row>
     <row r="228" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B228" s="34"/>
+      <c r="B228" s="32"/>
     </row>
     <row r="229" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B229" s="34"/>
+      <c r="B229" s="32"/>
     </row>
     <row r="230" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B230" s="34"/>
+      <c r="B230" s="32"/>
     </row>
     <row r="231" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B231" s="34"/>
+      <c r="B231" s="32"/>
     </row>
     <row r="232" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B232" s="34"/>
+      <c r="B232" s="32"/>
     </row>
     <row r="233" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B233" s="34"/>
+      <c r="B233" s="32"/>
     </row>
     <row r="234" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B234" s="34"/>
+      <c r="B234" s="32"/>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B235" s="34"/>
+      <c r="B235" s="32"/>
     </row>
     <row r="236" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B236" s="34"/>
+      <c r="B236" s="32"/>
     </row>
     <row r="237" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B237" s="34"/>
+      <c r="B237" s="32"/>
     </row>
     <row r="238" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B238" s="34"/>
+      <c r="B238" s="32"/>
     </row>
     <row r="239" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B239" s="34"/>
+      <c r="B239" s="32"/>
     </row>
     <row r="240" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B240" s="34"/>
+      <c r="B240" s="32"/>
     </row>
     <row r="241" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B241" s="34"/>
+      <c r="B241" s="32"/>
     </row>
     <row r="242" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B242" s="34"/>
+      <c r="B242" s="32"/>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B243" s="34"/>
+      <c r="B243" s="32"/>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B244" s="34"/>
+      <c r="B244" s="32"/>
     </row>
     <row r="245" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B245" s="34"/>
+      <c r="B245" s="32"/>
     </row>
     <row r="246" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B246" s="34"/>
+      <c r="B246" s="32"/>
     </row>
     <row r="247" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B247" s="34"/>
+      <c r="B247" s="32"/>
     </row>
     <row r="248" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B248" s="34"/>
+      <c r="B248" s="32"/>
     </row>
     <row r="249" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B249" s="34"/>
+      <c r="B249" s="32"/>
     </row>
     <row r="250" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B250" s="34"/>
+      <c r="B250" s="32"/>
     </row>
     <row r="251" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B251" s="34"/>
+      <c r="B251" s="32"/>
     </row>
     <row r="252" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B252" s="34"/>
+      <c r="B252" s="32"/>
     </row>
     <row r="253" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B253" s="34"/>
+      <c r="B253" s="32"/>
     </row>
     <row r="254" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B254" s="34"/>
+      <c r="B254" s="32"/>
     </row>
     <row r="255" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B255" s="34"/>
+      <c r="B255" s="32"/>
     </row>
     <row r="256" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B256" s="34"/>
+      <c r="B256" s="32"/>
     </row>
     <row r="257" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B257" s="34"/>
+      <c r="B257" s="32"/>
     </row>
     <row r="258" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B258" s="34"/>
+      <c r="B258" s="32"/>
     </row>
     <row r="259" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B259" s="34"/>
+      <c r="B259" s="32"/>
     </row>
     <row r="260" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B260" s="34"/>
+      <c r="B260" s="32"/>
     </row>
     <row r="261" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B261" s="34"/>
+      <c r="B261" s="32"/>
     </row>
     <row r="262" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B262" s="34"/>
+      <c r="B262" s="32"/>
     </row>
     <row r="263" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B263" s="34"/>
+      <c r="B263" s="32"/>
     </row>
     <row r="264" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B264" s="34"/>
+      <c r="B264" s="32"/>
     </row>
     <row r="265" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B265" s="34"/>
+      <c r="B265" s="32"/>
     </row>
     <row r="266" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B266" s="34"/>
+      <c r="B266" s="32"/>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B267" s="34"/>
+      <c r="B267" s="32"/>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B268" s="34"/>
+      <c r="B268" s="32"/>
     </row>
     <row r="269" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B269" s="34"/>
+      <c r="B269" s="32"/>
     </row>
     <row r="270" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B270" s="34"/>
+      <c r="B270" s="32"/>
     </row>
     <row r="271" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B271" s="34"/>
+      <c r="B271" s="32"/>
     </row>
     <row r="272" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B272" s="34"/>
+      <c r="B272" s="32"/>
     </row>
     <row r="273" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B273" s="34"/>
+      <c r="B273" s="32"/>
     </row>
     <row r="274" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B274" s="34"/>
+      <c r="B274" s="32"/>
     </row>
     <row r="275" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B275" s="34"/>
+      <c r="B275" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3245,127 +3210,127 @@
       <c r="E1" s="7"/>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="2:8" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="16" t="s">
+      <c r="F3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="19">
         <v>60</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="19">
         <v>0.25</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="19">
         <v>0</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>2</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="19">
         <v>300</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="19">
         <v>0.6</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="19">
         <v>0.1</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="20" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <v>3</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <v>300</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="22">
         <v>2</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <v>0.2</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B9" s="13"/>
@@ -3388,10 +3353,10 @@
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="13"/>
@@ -3401,10 +3366,10 @@
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>1</v>
       </c>
       <c r="D12" s="13"/>
@@ -3414,10 +3379,10 @@
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="33">
         <f>C12*60</f>
         <v>60</v>
       </c>
@@ -3428,10 +3393,10 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>3895.3</v>
       </c>
       <c r="D14" s="9"/>
@@ -3441,10 +3406,10 @@
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <v>66.5</v>
       </c>
       <c r="D15" s="13"/>
@@ -3454,10 +3419,10 @@
       <c r="H15" s="13"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="21">
+      <c r="B16" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="20">
         <f>IF(C15&lt;E4,F4,IF(C15&lt;E5,F5,F6))</f>
         <v>0.6</v>
       </c>
@@ -3468,49 +3433,49 @@
       <c r="H16" s="13"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B17" s="25" t="s">
-        <v>49</v>
+      <c r="B17" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="C17" s="11">
         <f>IF(C15&lt;E4,(C14/F4)/3600,IF(C15&lt;E5,(C14/F5)/3600,(C14/F6)/3600))</f>
         <v>1.8033796296296296</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>51</v>
+      <c r="D17" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="11">
         <f>IF(C15&lt;E4,G4,IF(C15&lt;E5,G5,G6))</f>
         <v>0.1</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>51</v>
+      <c r="D18" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <f>IF(C15&lt;E4,H4,IF(C15&lt;E5,C14/(4*F5*C13),C14/(F6*C13)))</f>
         <v>27.050694444444446</v>
       </c>
-      <c r="D19" s="15"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="28" t="s">
-        <v>46</v>
+      <c r="B20" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="C20" s="12">
         <f>IF(C19&gt;99,99,ROUND(C19,0))</f>
         <v>27</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>51</v>
+      <c r="D20" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/TSIG_Muskingum.xlsx
+++ b/file/table/TSIG_Muskingum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30014"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FC560D-F81B-492D-B105-949977941517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D873B0-AB2C-47AE-A9F6-9788C92FD4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{293BEA77-BE37-42CC-81CC-CF669E9BF0C2}"/>
   </bookViews>
@@ -62,12 +62,78 @@
         </r>
       </text>
     </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{BAD9FC86-2973-44E2-A13D-C8C3D8723E7C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tiempo de viaje</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{0E204287-C6F3-4D87-8554-D787DAADC3A6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Factor de ponderación</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{EF10BFC8-96BF-4275-8493-9117E042233A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Número de tramos para tránsito hidrológico</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{DB567B82-55A6-447C-AD7D-58F235138CDE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Validación de n &lt;= 99 tramos</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{82BC6F67-165F-4E95-9254-AD5FF2C532C5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Elevación o cota del centroide del río. 
+QGIS</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>≥ 300</t>
   </si>
@@ -229,6 +295,105 @@
     <t>Los datos de la longitud del cauce (L) se tomaron directamente del modelo geográfico desarrollado en GEO-HMS. Teniendo en cuenta las dificultades en el cálculo de las pendientes y en la determinación de la extensión en las planicies, se establecieron, con base en las pendientes medias de cada sector las siguientes velocidades de la onda de propagación: en la cuenca alta c=2 m/s, en la media c=0.6m/s y en la baja c=0.25m/s. Para estas estimaciones también se tuvieron en cuenta los tiempos observados entre los picos de los hidrogramas medidos y las observaciones cualitativas disponibles. 
 2. Factor de ponderación X: Este parámetro oscila entre X=0 para el embalse lineal, donde el mecanismo principal es el de almacenamiento, y por tanto una mayor atenuación de la creciente y X=0.5 para ondas puramente cinemáticas, donde no hay atenuación del hidrograma sino puramente translación. Teniendo en cuenta, que en la cuenca baja las pendientes son muy suaves y se presentan desbordamientos y flujos laterales en las planicies, se tomó X=0. Siguiendo recomendaciones generales, para cauces naturales, en la cuenca alta se fijó X=0.2 y un valor intermedio en la cuenca media, con X=0.1.
 3. Número de subtramos nx: El número de subtramos tiene una gran incidencia en la atenuación de los hidrogramas. A mayor número de subtramos, menor es la atenuación. Se puede demostrar que es proporcional al número de Courant cr. Para números de Courant menores que 1, las ecuaciones de la onda cinemática presentan atenuación numérica. En las mediciones hidrológicas disponibles, se puede apreciar una fuerte atenuación de los hidrogramas en la cuenca baja. Por consiguiente, la modelación en la parte baja debe reflejarlo y esto se logra con el menor número de pasos. Consecuentemente con lo anteriormente explicado y para obtener atenuaciones numéricas, en la cuenca baja se tomaron 2 subtramos, que corresponde a un número de Courant bajo. En la cuenca alta se calculó el número de tramos correspondiente al límite superior de las recomendaciones para el cr = 1:</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>reach_len</t>
+  </si>
+  <si>
+    <t>reach_rel</t>
+  </si>
+  <si>
+    <t>reach_sin</t>
+  </si>
+  <si>
+    <t>reach_slo</t>
+  </si>
+  <si>
+    <t>len_units</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Metre</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>cel_ms</t>
+  </si>
+  <si>
+    <t>COP30_1</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>n_eval</t>
+  </si>
+  <si>
+    <t>Arroyo El Zorro</t>
+  </si>
+  <si>
+    <t>Drenaje</t>
+  </si>
+  <si>
+    <t>Ejemplo para ríos HEC-HMS</t>
   </si>
 </sst>
 </file>
@@ -487,7 +652,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -585,6 +750,42 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="11" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3189,18 +3390,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767C5D59-0689-4C50-8389-33EC75A46DBF}">
-  <dimension ref="B1:H20"/>
+  <dimension ref="B1:N43"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.73046875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="17.1328125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
     <col min="3" max="3" width="18.73046875" style="10" customWidth="1"/>
     <col min="4" max="5" width="14.06640625" style="10" customWidth="1"/>
     <col min="6" max="6" width="10.86328125" style="9" customWidth="1"/>
     <col min="7" max="7" width="13.19921875" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.59765625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="19.86328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.3984375" style="9"/>
+    <col min="9" max="10" width="9.86328125" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="11.3984375" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
@@ -3210,15 +3411,15 @@
       <c r="E1" s="7"/>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="2:8" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B3" s="16" t="s">
@@ -3253,13 +3454,13 @@
       <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="44">
         <v>60</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="44">
         <v>0.25</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="44">
         <v>0</v>
       </c>
       <c r="H4" s="20">
@@ -3276,13 +3477,13 @@
       <c r="D5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="44">
         <v>300</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="44">
         <v>0.6</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="44">
         <v>0.1</v>
       </c>
       <c r="H5" s="20" t="s">
@@ -3299,13 +3500,13 @@
       <c r="D6" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="45">
         <v>300</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="45">
         <v>2</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="45">
         <v>0.2</v>
       </c>
       <c r="H6" s="23" t="s">
@@ -3313,24 +3514,24 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B9" s="13"/>
@@ -3397,7 +3598,7 @@
         <v>21</v>
       </c>
       <c r="C14" s="25">
-        <v>3895.3</v>
+        <v>9750.4755283144204</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="13"/>
@@ -3410,7 +3611,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="25">
-        <v>66.5</v>
+        <v>82.232498168945298</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -3423,7 +3624,7 @@
         <v>46</v>
       </c>
       <c r="C16" s="20">
-        <f>IF(C15&lt;E4,F4,IF(C15&lt;E5,F5,F6))</f>
+        <f>IF(C15&lt;$E$4,$F$4,IF(C15&lt;$E$5,$F$5,$F$6))</f>
         <v>0.6</v>
       </c>
       <c r="D16" s="13"/>
@@ -3432,51 +3633,986 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B17" s="24" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="11">
-        <f>IF(C15&lt;E4,(C14/F4)/3600,IF(C15&lt;E5,(C14/F5)/3600,(C14/F6)/3600))</f>
-        <v>1.8033796296296296</v>
+        <f>IF(C15&lt;$E$4,(C14/$F$4)/3600,IF(C15&lt;$E$5,(C14/$F$5)/3600,(C14/$F$6)/3600))</f>
+        <v>4.5141090408863063</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B18" s="24" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="11">
-        <f>IF(C15&lt;E4,G4,IF(C15&lt;E5,G5,G6))</f>
+        <f>IF(C15&lt;$E$4,$G$4,IF(C15&lt;$E$5,$G$5,$G$6))</f>
         <v>0.1</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" s="29" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="30">
-        <f>IF(C15&lt;E4,H4,IF(C15&lt;E5,C14/(4*F5*C13),C14/(F6*C13)))</f>
-        <v>27.050694444444446</v>
+        <f>ROUND(IF(C15&lt;$E$4,$H$4,IF(C15&lt;$E$5,C14/(4*$F$5*C13),C14/($F$6*C13))),0)</f>
+        <v>68</v>
       </c>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="27" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="12">
-        <f>IF(C19&gt;99,99,ROUND(C19,0))</f>
-        <v>27</v>
+        <f>IF(C19&gt;99,99,IF(C19=0,1,C19))</f>
+        <v>68</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B22" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B23" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="M23" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" s="41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B24" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="35">
+        <v>1052.6874419186299</v>
+      </c>
+      <c r="E24" s="35">
+        <v>3.9596557617188E-2</v>
+      </c>
+      <c r="F24" s="35">
+        <v>1.09776265346198</v>
+      </c>
+      <c r="G24" s="42">
+        <v>3.7614733529000002E-5</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="35">
+        <v>82.146202087402301</v>
+      </c>
+      <c r="J24" s="34">
+        <f>IF(I24&lt;$E$4,$F$4,IF(I24&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="K24" s="34">
+        <f>ROUND(IF(I24&lt;$E$4,$H$4,IF(I24&lt;$E$5,D24/(4*$F$5*$C$13),D24/($F$6*$C$13))),0)</f>
+        <v>7</v>
+      </c>
+      <c r="L24" s="34">
+        <f t="shared" ref="L24:L42" si="0">IF(I24&lt;$E$4,(D24/$F$4)/3600,IF(I24&lt;$E$5,(D24/$F$5)/3600,(D24/$F$6)/3600))</f>
+        <v>0.4873552971845509</v>
+      </c>
+      <c r="M24" s="34">
+        <f t="shared" ref="M24:M42" si="1">IF(I24&lt;$E$4,$G$4,IF(I24&lt;$E$5,$G$5,$G$6))</f>
+        <v>0.1</v>
+      </c>
+      <c r="N24" s="11">
+        <f>IF(K24&gt;99,99,IF(K24=0,1,K24))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B25" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="35">
+        <v>2214.3688792489802</v>
+      </c>
+      <c r="E25" s="35">
+        <v>5.0150680541992196</v>
+      </c>
+      <c r="F25" s="35">
+        <v>1.15260976611237</v>
+      </c>
+      <c r="G25" s="35">
+        <v>2.2647843822209998E-3</v>
+      </c>
+      <c r="H25" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="35">
+        <v>83.661056518554702</v>
+      </c>
+      <c r="J25" s="34">
+        <f>IF(I25&lt;$E$4,$F$4,IF(I25&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="K25" s="34">
+        <f>ROUND(IF(I25&lt;$E$4,$H$4,IF(I25&lt;$E$5,D25/(4*$F$5*$C$13),D25/($F$6*$C$13))),0)</f>
+        <v>15</v>
+      </c>
+      <c r="L25" s="34">
+        <f t="shared" si="0"/>
+        <v>1.0251707774300836</v>
+      </c>
+      <c r="M25" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="11">
+        <f t="shared" ref="N25:N42" si="2">IF(K25&gt;99,99,IF(K25=0,1,K25))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B26" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="35">
+        <v>812.52503404213098</v>
+      </c>
+      <c r="E26" s="35">
+        <v>4.2198181152343697</v>
+      </c>
+      <c r="F26" s="35">
+        <v>1.09971027809434</v>
+      </c>
+      <c r="G26" s="35">
+        <v>5.1934622792380002E-3</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="35">
+        <v>84.264968872070298</v>
+      </c>
+      <c r="J26" s="34">
+        <f>IF(I26&lt;$E$4,$F$4,IF(I26&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="K26" s="34">
+        <f>ROUND(IF(I26&lt;$E$4,$H$4,IF(I26&lt;$E$5,D26/(4*$F$5*$C$13),D26/($F$6*$C$13))),0)</f>
+        <v>6</v>
+      </c>
+      <c r="L26" s="34">
+        <f t="shared" si="0"/>
+        <v>0.37616899724172737</v>
+      </c>
+      <c r="M26" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N26" s="11">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B27" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="35">
+        <v>306.792701376602</v>
+      </c>
+      <c r="E27" s="35">
+        <v>1.7322082519531199</v>
+      </c>
+      <c r="F27" s="35">
+        <v>1</v>
+      </c>
+      <c r="G27" s="35">
+        <v>5.6461846849050002E-3</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="35">
+        <v>81.087654113769503</v>
+      </c>
+      <c r="J27" s="34">
+        <f>IF(I27&lt;$E$4,$F$4,IF(I27&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="K27" s="34">
+        <f>ROUND(IF(I27&lt;$E$4,$H$4,IF(I27&lt;$E$5,D27/(4*$F$5*$C$13),D27/($F$6*$C$13))),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L27" s="34">
+        <f t="shared" si="0"/>
+        <v>0.14203365804472315</v>
+      </c>
+      <c r="M27" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N27" s="11">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B28" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="35">
+        <v>3138.1446037980099</v>
+      </c>
+      <c r="E28" s="35">
+        <v>10.493408203125</v>
+      </c>
+      <c r="F28" s="35">
+        <v>1.1900200162855299</v>
+      </c>
+      <c r="G28" s="35">
+        <v>3.343825581022E-3</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="35">
+        <v>83.017272949218807</v>
+      </c>
+      <c r="J28" s="34">
+        <f>IF(I28&lt;$E$4,$F$4,IF(I28&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="K28" s="34">
+        <f>ROUND(IF(I28&lt;$E$4,$H$4,IF(I28&lt;$E$5,D28/(4*$F$5*$C$13),D28/($F$6*$C$13))),0)</f>
+        <v>22</v>
+      </c>
+      <c r="L28" s="34">
+        <f t="shared" si="0"/>
+        <v>1.4528447239805602</v>
+      </c>
+      <c r="M28" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B29" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="35">
+        <v>1504.4308351914499</v>
+      </c>
+      <c r="E29" s="35">
+        <v>1.16963958740234</v>
+      </c>
+      <c r="F29" s="35">
+        <v>1.2120932311380499</v>
+      </c>
+      <c r="G29" s="35">
+        <v>7.7746318411100004E-4</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="35">
+        <v>90.837333679199205</v>
+      </c>
+      <c r="J29" s="34">
+        <f t="shared" ref="J29:J42" si="3">IF(I29&lt;$E$4,$F$4,IF(I29&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="K29" s="34">
+        <f t="shared" ref="K29:K42" si="4">ROUND(IF(I29&lt;$E$4,$H$4,IF(I29&lt;$E$5,D29/(4*$F$5*$C$13),D29/($F$6*$C$13))),0)</f>
+        <v>10</v>
+      </c>
+      <c r="L29" s="34">
+        <f t="shared" si="0"/>
+        <v>0.69649575703307876</v>
+      </c>
+      <c r="M29" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B30" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="35">
+        <v>480.31346950722002</v>
+      </c>
+      <c r="E30" s="35">
+        <v>7.86087799072265</v>
+      </c>
+      <c r="F30" s="35">
+        <v>1.16696962122673</v>
+      </c>
+      <c r="G30" s="35">
+        <v>1.6366141051151001E-2</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="35">
+        <v>98.604133605957003</v>
+      </c>
+      <c r="J30" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K30" s="34">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="L30" s="34">
+        <f t="shared" si="0"/>
+        <v>0.22236734699408336</v>
+      </c>
+      <c r="M30" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N30" s="11">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B31" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="35">
+        <v>2007.8383952873301</v>
+      </c>
+      <c r="E31" s="35">
+        <v>3.1578063964844E-2</v>
+      </c>
+      <c r="F31" s="35">
+        <v>1.0778579614880499</v>
+      </c>
+      <c r="G31" s="42">
+        <v>1.5727393220000002E-5</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="35">
+        <v>98.528877258300795</v>
+      </c>
+      <c r="J31" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K31" s="34">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="L31" s="34">
+        <f t="shared" si="0"/>
+        <v>0.9295548126330232</v>
+      </c>
+      <c r="M31" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N31" s="11">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B32" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="35">
+        <v>4419.1284818909598</v>
+      </c>
+      <c r="E32" s="35">
+        <v>6.0207214355468697</v>
+      </c>
+      <c r="F32" s="35">
+        <v>1.22495673931062</v>
+      </c>
+      <c r="G32" s="35">
+        <v>1.3624228080760001E-3</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="35">
+        <v>106.842567443848</v>
+      </c>
+      <c r="J32" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K32" s="34">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="L32" s="34">
+        <f t="shared" si="0"/>
+        <v>2.0458928156902592</v>
+      </c>
+      <c r="M32" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N32" s="11">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B33" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="35">
+        <v>9750.4755283144204</v>
+      </c>
+      <c r="E33" s="35">
+        <v>13.3757553100585</v>
+      </c>
+      <c r="F33" s="35">
+        <v>1.2673326759994901</v>
+      </c>
+      <c r="G33" s="35">
+        <v>1.371805433614E-3</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="35">
+        <v>82.232498168945298</v>
+      </c>
+      <c r="J33" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K33" s="34">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="L33" s="34">
+        <f t="shared" si="0"/>
+        <v>4.5141090408863063</v>
+      </c>
+      <c r="M33" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N33" s="11">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B34" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="35">
+        <v>1948.7592425986099</v>
+      </c>
+      <c r="E34" s="35">
+        <v>5.8508758544921804</v>
+      </c>
+      <c r="F34" s="35">
+        <v>1.46329755411188</v>
+      </c>
+      <c r="G34" s="35">
+        <v>3.0023595150159999E-3</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="35">
+        <v>78.631752014160199</v>
+      </c>
+      <c r="J34" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K34" s="34">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="L34" s="34">
+        <f t="shared" si="0"/>
+        <v>0.90220335305491206</v>
+      </c>
+      <c r="M34" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N34" s="11">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B35" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="35">
+        <v>6791.2766201920904</v>
+      </c>
+      <c r="E35" s="35">
+        <v>18.292015075683501</v>
+      </c>
+      <c r="F35" s="35">
+        <v>1.1682867633829599</v>
+      </c>
+      <c r="G35" s="35">
+        <v>2.6934575189140001E-3</v>
+      </c>
+      <c r="H35" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I35" s="35">
+        <v>87.634117126464801</v>
+      </c>
+      <c r="J35" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K35" s="34">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+      <c r="L35" s="34">
+        <f t="shared" si="0"/>
+        <v>3.1441095463852271</v>
+      </c>
+      <c r="M35" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N35" s="11">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B36" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="35">
+        <v>4676.4115953257196</v>
+      </c>
+      <c r="E36" s="35">
+        <v>36.208351135253899</v>
+      </c>
+      <c r="F36" s="35">
+        <v>1.2637308364015001</v>
+      </c>
+      <c r="G36" s="35">
+        <v>7.7427639541920003E-3</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I36" s="35">
+        <v>109.323036193848</v>
+      </c>
+      <c r="J36" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K36" s="34">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="L36" s="34">
+        <f t="shared" si="0"/>
+        <v>2.1650053682063519</v>
+      </c>
+      <c r="M36" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N36" s="11">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B37" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="35">
+        <v>2346.7349482674599</v>
+      </c>
+      <c r="E37" s="35">
+        <v>15.4802093505859</v>
+      </c>
+      <c r="F37" s="35">
+        <v>1.2662899618863199</v>
+      </c>
+      <c r="G37" s="35">
+        <v>6.5964881811700002E-3</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" s="35">
+        <v>136.53871154785199</v>
+      </c>
+      <c r="J37" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K37" s="34">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="L37" s="34">
+        <f t="shared" si="0"/>
+        <v>1.0864513649386389</v>
+      </c>
+      <c r="M37" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N37" s="11">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B38" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="35">
+        <v>4554.9148638168299</v>
+      </c>
+      <c r="E38" s="35">
+        <v>29.3015747070312</v>
+      </c>
+      <c r="F38" s="35">
+        <v>1.5905670202208699</v>
+      </c>
+      <c r="G38" s="35">
+        <v>6.4329577133910004E-3</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="35">
+        <v>109.91001129150401</v>
+      </c>
+      <c r="J38" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K38" s="34">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="L38" s="34">
+        <f t="shared" si="0"/>
+        <v>2.1087568813966806</v>
+      </c>
+      <c r="M38" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N38" s="11">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B39" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="35">
+        <v>8468.1780681584405</v>
+      </c>
+      <c r="E39" s="35">
+        <v>7.6516380310058603</v>
+      </c>
+      <c r="F39" s="35">
+        <v>1.21591229968776</v>
+      </c>
+      <c r="G39" s="35">
+        <v>9.0357547626199999E-4</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" s="35">
+        <v>62.740562438964801</v>
+      </c>
+      <c r="J39" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K39" s="34">
+        <f t="shared" si="4"/>
+        <v>59</v>
+      </c>
+      <c r="L39" s="34">
+        <f t="shared" si="0"/>
+        <v>3.9204528093326112</v>
+      </c>
+      <c r="M39" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N39" s="11">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B40" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="35">
+        <v>5567.3194321154397</v>
+      </c>
+      <c r="E40" s="35">
+        <v>8.62030029296875</v>
+      </c>
+      <c r="F40" s="35">
+        <v>1.2950148610724099</v>
+      </c>
+      <c r="G40" s="35">
+        <v>1.5483753713219999E-3</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" s="35">
+        <v>69.165557861328097</v>
+      </c>
+      <c r="J40" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K40" s="34">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+      <c r="L40" s="34">
+        <f t="shared" si="0"/>
+        <v>2.5774627000534442</v>
+      </c>
+      <c r="M40" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N40" s="11">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B41" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="35">
+        <v>1544.7590937973901</v>
+      </c>
+      <c r="E41" s="35">
+        <v>2.1586227416992099</v>
+      </c>
+      <c r="F41" s="35">
+        <v>1.2910739843402099</v>
+      </c>
+      <c r="G41" s="35">
+        <v>1.3973847121969999E-3</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I41" s="35">
+        <v>73.386154174804702</v>
+      </c>
+      <c r="J41" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K41" s="34">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="L41" s="34">
+        <f t="shared" si="0"/>
+        <v>0.71516624712842136</v>
+      </c>
+      <c r="M41" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N41" s="11">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B42" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="35">
+        <v>3047.0183307345601</v>
+      </c>
+      <c r="E42" s="35">
+        <v>1.8390045166015601</v>
+      </c>
+      <c r="F42" s="35">
+        <v>1.4072559008632799</v>
+      </c>
+      <c r="G42" s="35">
+        <v>6.0354232137399999E-4</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I42" s="35">
+        <v>78.397857666015597</v>
+      </c>
+      <c r="J42" s="34">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K42" s="34">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="L42" s="34">
+        <f t="shared" si="0"/>
+        <v>1.4106566345993334</v>
+      </c>
+      <c r="M42" s="34">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="N42" s="11">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B43" s="37"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3484,7 +4620,8 @@
     <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/file/table/TSIG_Muskingum.xlsx
+++ b/file/table/TSIG_Muskingum.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D873B0-AB2C-47AE-A9F6-9788C92FD4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6851D60-31AE-4AFA-8029-7B0C3AA300B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{293BEA77-BE37-42CC-81CC-CF669E9BF0C2}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" activeTab="3" xr2:uid="{293BEA77-BE37-42CC-81CC-CF669E9BF0C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="5" r:id="rId1"/>
-    <sheet name="Texto" sheetId="6" r:id="rId2"/>
-    <sheet name="Calculo" sheetId="1" r:id="rId3"/>
-    <sheet name="{R}" sheetId="3" r:id="rId4"/>
+    <sheet name="Text" sheetId="6" r:id="rId2"/>
+    <sheet name="ByElevationRange" sheetId="1" r:id="rId3"/>
+    <sheet name="BySlopeRange" sheetId="7" r:id="rId4"/>
+    <sheet name="{R}" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Database" localSheetId="0">#REF!</definedName>
@@ -132,8 +133,97 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Test</author>
+  </authors>
+  <commentList>
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{1EC9D16D-0ECD-4F28-AB90-A7882B555676}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Salto de tiempo de modelación en HEC-HMS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{0C1084D6-D8E8-4F43-8B30-FAF80F724CCE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tiempo de viaje</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{6A01C541-3BA5-43E2-93FC-BAC4A9CA14F3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Factor de ponderación</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{1C7361BE-A80D-40C5-A1DB-609BD5A454C2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Número de tramos para tránsito hidrológico</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{8E7A5DFE-D730-4546-9117-8E413564F6C4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Validación de n &lt;= 99 tramos</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{151A73C9-13A9-4429-89A0-E1297F9BDF47}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Elevación o cota del centroide del río. 
+QGIS</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>≥ 300</t>
   </si>
@@ -190,9 +280,6 @@
   </si>
   <si>
     <t>L / (c * Δt)</t>
-  </si>
-  <si>
-    <t>Reclasificación del mapa de elevaciones para la definición de zonas topográficas y parámetros Muskingum</t>
   </si>
   <si>
     <t>Ejemplo para un río</t>
@@ -394,6 +481,30 @@
   </si>
   <si>
     <t>Ejemplo para ríos HEC-HMS</t>
+  </si>
+  <si>
+    <t>Pendiente (m/m)</t>
+  </si>
+  <si>
+    <t>Rango de pendiente (m/m)</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>s &lt; 0.001</t>
+  </si>
+  <si>
+    <t>0.001 ≤ cota &lt; 0.02</t>
+  </si>
+  <si>
+    <t>≥ 0.02</t>
+  </si>
+  <si>
+    <t>Parámetros Muskingum a partir de la pendiente del cauce</t>
+  </si>
+  <si>
+    <t>Parámetros Muskingum a partir de la reclasificación de zonas topográficas</t>
   </si>
 </sst>
 </file>
@@ -1687,851 +1798,851 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AC4D5E-A305-4BD9-9483-CE4857D35E84}">
   <dimension ref="B2:B274"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.1171875" defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="4.1328125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="107.46484375" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="9.1328125" style="31"/>
+    <col min="1" max="1" width="4.1171875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="107.46875" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="9.1171875" style="31"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B2" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B4" s="32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B5" s="31"/>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.65">
+      <c r="B6" s="32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B5" s="31"/>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B6" s="32" t="s">
+    <row r="7" spans="2:2" ht="47.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B7" s="31"/>
+    </row>
+    <row r="8" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
+      <c r="B8" s="32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="47.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="31"/>
-    </row>
-    <row r="8" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B8" s="32" t="s">
+    <row r="9" spans="2:2" ht="48" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B9" s="31"/>
+    </row>
+    <row r="10" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
+      <c r="B10" s="32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="48" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="31"/>
-    </row>
-    <row r="10" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B10" s="32" t="s">
+    <row r="11" spans="2:2" ht="159" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B11" s="32"/>
+    </row>
+    <row r="12" spans="2:2" ht="49" x14ac:dyDescent="0.65">
+      <c r="B12" s="32" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="159" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B11" s="32"/>
-    </row>
-    <row r="12" spans="2:2" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B12" s="32" t="s">
+    <row r="13" spans="2:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B13" s="32"/>
+    </row>
+    <row r="14" spans="2:2" ht="49" x14ac:dyDescent="0.65">
+      <c r="B14" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B13" s="32"/>
-    </row>
-    <row r="14" spans="2:2" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B14" s="32" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.65">
+      <c r="B15" s="32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B15" s="32" t="s">
+    <row r="16" spans="2:2" ht="39" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B16" s="32"/>
+    </row>
+    <row r="17" spans="2:2" ht="81.7" x14ac:dyDescent="0.65">
+      <c r="B17" s="32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="39" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B16" s="32"/>
-    </row>
-    <row r="17" spans="2:2" ht="82.5" x14ac:dyDescent="0.6">
-      <c r="B17" s="32" t="s">
+    <row r="18" spans="2:2" ht="138.75" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B18" s="32"/>
+    </row>
+    <row r="19" spans="2:2" ht="49" x14ac:dyDescent="0.65">
+      <c r="B19" s="32" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="138.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B18" s="32"/>
-    </row>
-    <row r="19" spans="2:2" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B19" s="32" t="s">
+    <row r="20" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
+      <c r="B20" s="32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B20" s="32" t="s">
+    <row r="21" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B21" s="32"/>
+    </row>
+    <row r="22" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
+      <c r="B22" s="32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B21" s="32"/>
-    </row>
-    <row r="22" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B22" s="32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B23" s="32"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B24" s="32"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B25" s="32"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B26" s="32"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B27" s="32"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B28" s="32"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B29" s="32"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B30" s="32"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B31" s="32"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B32" s="32"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B33" s="32"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B34" s="32"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B35" s="32"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B36" s="32"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B37" s="32"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B38" s="32"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B39" s="32"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B40" s="32"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B41" s="32"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B42" s="32"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B43" s="32"/>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B44" s="32"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B45" s="32"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B46" s="32"/>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B47" s="32"/>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B48" s="32"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B49" s="32"/>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B50" s="32"/>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B51" s="32"/>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B52" s="32"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B53" s="32"/>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B54" s="32"/>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B55" s="32"/>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B56" s="32"/>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B57" s="32"/>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B58" s="32"/>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B59" s="32"/>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B60" s="32"/>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B61" s="32"/>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B62" s="32"/>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B63" s="32"/>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B64" s="32"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B65" s="32"/>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B66" s="32"/>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B67" s="32"/>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B68" s="32"/>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B69" s="32"/>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B70" s="32"/>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B71" s="32"/>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B72" s="32"/>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B73" s="32"/>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B74" s="32"/>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B75" s="32"/>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B76" s="32"/>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B77" s="32"/>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B78" s="32"/>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B79" s="32"/>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B80" s="32"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B81" s="32"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B82" s="32"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B83" s="32"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B84" s="32"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B85" s="32"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B86" s="32"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B87" s="32"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B88" s="32"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B89" s="32"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B90" s="32"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B91" s="32"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B92" s="32"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B93" s="32"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B94" s="32"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B95" s="32"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B96" s="32"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B97" s="32"/>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B98" s="32"/>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B99" s="32"/>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B100" s="32"/>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B101" s="32"/>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B102" s="32"/>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B103" s="32"/>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B104" s="32"/>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B105" s="32"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B106" s="32"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B107" s="32"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B108" s="32"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B109" s="32"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B110" s="32"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B111" s="32"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B112" s="32"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B113" s="32"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B114" s="32"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B115" s="32"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B116" s="32"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B117" s="32"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B118" s="32"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B119" s="32"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B120" s="32"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B121" s="32"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B122" s="32"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B123" s="32"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B124" s="32"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B125" s="32"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B126" s="32"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B127" s="32"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B128" s="32"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B129" s="32"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B130" s="32"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B131" s="32"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B132" s="32"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B133" s="32"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B134" s="32"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B135" s="32"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B136" s="32"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B137" s="32"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B138" s="32"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B139" s="32"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B140" s="32"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B141" s="32"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B142" s="32"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B143" s="32"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B144" s="32"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B145" s="32"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B146" s="32"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B147" s="32"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B148" s="32"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B149" s="32"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B150" s="32"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B151" s="32"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B152" s="32"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B153" s="32"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B154" s="32"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B155" s="32"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B156" s="32"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B157" s="32"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B158" s="32"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B159" s="32"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B160" s="32"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B161" s="32"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B162" s="32"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B163" s="32"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B164" s="32"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B165" s="32"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B166" s="32"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B167" s="32"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B168" s="32"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B169" s="32"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B170" s="32"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B171" s="32"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B172" s="32"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B173" s="32"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B174" s="32"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B175" s="32"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B176" s="32"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B177" s="32"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B178" s="32"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B179" s="32"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B180" s="32"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B181" s="32"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B182" s="32"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B183" s="32"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B184" s="32"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B185" s="32"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B186" s="32"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B187" s="32"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B188" s="32"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B189" s="32"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B190" s="32"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B191" s="32"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B192" s="32"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B193" s="32"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B194" s="32"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B195" s="32"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B196" s="32"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B197" s="32"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B198" s="32"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B199" s="32"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B200" s="32"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B201" s="32"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B202" s="32"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B203" s="32"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B204" s="32"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B205" s="32"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B206" s="32"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B207" s="32"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B208" s="32"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B209" s="32"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B210" s="32"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B211" s="32"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B212" s="32"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B213" s="32"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B214" s="32"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B215" s="32"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B216" s="32"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B217" s="32"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B218" s="32"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B219" s="32"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B220" s="32"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B221" s="32"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B222" s="32"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B223" s="32"/>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B224" s="32"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B225" s="32"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B226" s="32"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B227" s="32"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B228" s="32"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B229" s="32"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B230" s="32"/>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B231" s="32"/>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B232" s="32"/>
     </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B233" s="32"/>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B234" s="32"/>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B235" s="32"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B236" s="32"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B237" s="32"/>
     </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B238" s="32"/>
     </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B239" s="32"/>
     </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B240" s="32"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B241" s="32"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B242" s="32"/>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B243" s="32"/>
     </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B244" s="32"/>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B245" s="32"/>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B246" s="32"/>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B247" s="32"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B248" s="32"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B249" s="32"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B250" s="32"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B251" s="32"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="252" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B252" s="32"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="253" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B253" s="32"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B254" s="32"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B255" s="32"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B256" s="32"/>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="257" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B257" s="32"/>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B258" s="32"/>
     </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="259" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B259" s="32"/>
     </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="260" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B260" s="32"/>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B261" s="32"/>
     </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B262" s="32"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B263" s="32"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B264" s="32"/>
     </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="265" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B265" s="32"/>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="266" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B266" s="32"/>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="267" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B267" s="32"/>
     </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="268" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B268" s="32"/>
     </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="269" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B269" s="32"/>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="270" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B270" s="32"/>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B271" s="32"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B272" s="32"/>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B273" s="32"/>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B274" s="32"/>
     </row>
   </sheetData>
@@ -2544,841 +2655,841 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7BD45F-4FE9-4579-9909-3C8323EFA84F}">
   <dimension ref="B2:B275"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.1171875" defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="4.1328125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="107.46484375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="31" customWidth="1"/>
-    <col min="4" max="16384" width="9.1328125" style="31"/>
+    <col min="1" max="1" width="4.1171875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="107.46875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="5.3515625" style="31" customWidth="1"/>
+    <col min="4" max="16384" width="9.1171875" style="31"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="82.5" x14ac:dyDescent="0.6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="81.7" x14ac:dyDescent="0.65">
       <c r="B4" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.65">
+      <c r="B5" s="32"/>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.65">
+      <c r="B6" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B7" s="32"/>
+    </row>
+    <row r="8" spans="2:2" ht="326.7" x14ac:dyDescent="0.65">
+      <c r="B8" s="32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B9" s="32"/>
+    </row>
+    <row r="10" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
+      <c r="B10" s="32" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B5" s="32"/>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.6">
-      <c r="B6" s="32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="32"/>
-    </row>
-    <row r="8" spans="2:2" ht="330" x14ac:dyDescent="0.6">
-      <c r="B8" s="32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="32"/>
-    </row>
-    <row r="10" spans="2:2" ht="33" x14ac:dyDescent="0.6">
-      <c r="B10" s="32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B11" s="32"/>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B12" s="32"/>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B13" s="32"/>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B14" s="32"/>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B15" s="32"/>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B16" s="32"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B17" s="32"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B18" s="32"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B19" s="32"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B20" s="32"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B21" s="32"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B22" s="32"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B23" s="32"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B24" s="32"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B25" s="32"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B26" s="32"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B27" s="32"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B28" s="32"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B29" s="32"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B30" s="32"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B31" s="32"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B32" s="32"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B33" s="32"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B34" s="32"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B35" s="32"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B36" s="32"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B37" s="32"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B38" s="32"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B39" s="32"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B40" s="32"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B41" s="32"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B42" s="32"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B43" s="32"/>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B44" s="32"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B45" s="32"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B46" s="32"/>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B47" s="32"/>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B48" s="32"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B49" s="32"/>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B50" s="32"/>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B51" s="32"/>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B52" s="32"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B53" s="32"/>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B54" s="32"/>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B55" s="32"/>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B56" s="32"/>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B57" s="32"/>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B58" s="32"/>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B59" s="32"/>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B60" s="32"/>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B61" s="32"/>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B62" s="32"/>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B63" s="32"/>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B64" s="32"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B65" s="32"/>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B66" s="32"/>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B67" s="32"/>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B68" s="32"/>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B69" s="32"/>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B70" s="32"/>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B71" s="32"/>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B72" s="32"/>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B73" s="32"/>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B74" s="32"/>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B75" s="32"/>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B76" s="32"/>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B77" s="32"/>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B78" s="32"/>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B79" s="32"/>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B80" s="32"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B81" s="32"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B82" s="32"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B83" s="32"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B84" s="32"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B85" s="32"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B86" s="32"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B87" s="32"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B88" s="32"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B89" s="32"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B90" s="32"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B91" s="32"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B92" s="32"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B93" s="32"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B94" s="32"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B95" s="32"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B96" s="32"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B97" s="32"/>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B98" s="32"/>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B99" s="32"/>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B100" s="32"/>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B101" s="32"/>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B102" s="32"/>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B103" s="32"/>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B104" s="32"/>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B105" s="32"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B106" s="32"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B107" s="32"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B108" s="32"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B109" s="32"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B110" s="32"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B111" s="32"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B112" s="32"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B113" s="32"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B114" s="32"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B115" s="32"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B116" s="32"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B117" s="32"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B118" s="32"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B119" s="32"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B120" s="32"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B121" s="32"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B122" s="32"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B123" s="32"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B124" s="32"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B125" s="32"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B126" s="32"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B127" s="32"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B128" s="32"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B129" s="32"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B130" s="32"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B131" s="32"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B132" s="32"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B133" s="32"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B134" s="32"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B135" s="32"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B136" s="32"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B137" s="32"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B138" s="32"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B139" s="32"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B140" s="32"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B141" s="32"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B142" s="32"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B143" s="32"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B144" s="32"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B145" s="32"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B146" s="32"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B147" s="32"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B148" s="32"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B149" s="32"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B150" s="32"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B151" s="32"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B152" s="32"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B153" s="32"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B154" s="32"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B155" s="32"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B156" s="32"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B157" s="32"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B158" s="32"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B159" s="32"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B160" s="32"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B161" s="32"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B162" s="32"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B163" s="32"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B164" s="32"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B165" s="32"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B166" s="32"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B167" s="32"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B168" s="32"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B169" s="32"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B170" s="32"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B171" s="32"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B172" s="32"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B173" s="32"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B174" s="32"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B175" s="32"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B176" s="32"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B177" s="32"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B178" s="32"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B179" s="32"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B180" s="32"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B181" s="32"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B182" s="32"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B183" s="32"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B184" s="32"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B185" s="32"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B186" s="32"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B187" s="32"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B188" s="32"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B189" s="32"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B190" s="32"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B191" s="32"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B192" s="32"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B193" s="32"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B194" s="32"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B195" s="32"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B196" s="32"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B197" s="32"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B198" s="32"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B199" s="32"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B200" s="32"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B201" s="32"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B202" s="32"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B203" s="32"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B204" s="32"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B205" s="32"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B206" s="32"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B207" s="32"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B208" s="32"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B209" s="32"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B210" s="32"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B211" s="32"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B212" s="32"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B213" s="32"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B214" s="32"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B215" s="32"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B216" s="32"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B217" s="32"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B218" s="32"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B219" s="32"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B220" s="32"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B221" s="32"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B222" s="32"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B223" s="32"/>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B224" s="32"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B225" s="32"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B226" s="32"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B227" s="32"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B228" s="32"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B229" s="32"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B230" s="32"/>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B231" s="32"/>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B232" s="32"/>
     </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B233" s="32"/>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B234" s="32"/>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B235" s="32"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B236" s="32"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B237" s="32"/>
     </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B238" s="32"/>
     </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B239" s="32"/>
     </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B240" s="32"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B241" s="32"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B242" s="32"/>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B243" s="32"/>
     </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B244" s="32"/>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B245" s="32"/>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B246" s="32"/>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="247" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B247" s="32"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B248" s="32"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B249" s="32"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B250" s="32"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B251" s="32"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="252" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B252" s="32"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="253" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B253" s="32"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B254" s="32"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B255" s="32"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B256" s="32"/>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="257" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B257" s="32"/>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B258" s="32"/>
     </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="259" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B259" s="32"/>
     </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="260" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B260" s="32"/>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="261" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B261" s="32"/>
     </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B262" s="32"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B263" s="32"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B264" s="32"/>
     </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="265" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B265" s="32"/>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="266" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B266" s="32"/>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="267" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B267" s="32"/>
     </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="268" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B268" s="32"/>
     </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="269" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B269" s="32"/>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="270" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B270" s="32"/>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B271" s="32"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B272" s="32"/>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B273" s="32"/>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B274" s="32"/>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B275" s="32"/>
     </row>
   </sheetData>
@@ -3391,28 +3502,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767C5D59-0689-4C50-8389-33EC75A46DBF}">
   <dimension ref="B1:N43"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.41015625" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="18.73046875" style="10" customWidth="1"/>
-    <col min="4" max="5" width="14.06640625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.86328125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="13.19921875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.59765625" style="9" customWidth="1"/>
-    <col min="9" max="10" width="9.86328125" style="9" customWidth="1"/>
-    <col min="11" max="16384" width="11.3984375" style="9"/>
+    <col min="1" max="1" width="2.703125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="15.64453125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18.703125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14.05859375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="10.64453125" style="10" customWidth="1"/>
+    <col min="6" max="7" width="10.64453125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12.64453125" style="9" customWidth="1"/>
+    <col min="9" max="14" width="10.64453125" style="9" customWidth="1"/>
+    <col min="15" max="16384" width="11.41015625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.5">
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="46" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C2" s="46"/>
       <c r="D2" s="46"/>
@@ -3421,7 +3532,7 @@
       <c r="G2" s="46"/>
       <c r="H2" s="46"/>
     </row>
-    <row r="3" spans="2:8" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" ht="30" x14ac:dyDescent="0.5">
       <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
@@ -3429,13 +3540,13 @@
         <v>6</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>15</v>
@@ -3444,7 +3555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B4" s="18">
         <v>1</v>
       </c>
@@ -3467,7 +3578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B5" s="18">
         <v>2</v>
       </c>
@@ -3490,7 +3601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B6" s="21">
         <v>3</v>
       </c>
@@ -3513,7 +3624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B7" s="46" t="s">
         <v>14</v>
       </c>
@@ -3524,7 +3635,7 @@
       <c r="G7" s="46"/>
       <c r="H7" s="46"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
       <c r="D8" s="46"/>
@@ -3533,7 +3644,7 @@
       <c r="G8" s="46"/>
       <c r="H8" s="46"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -3542,9 +3653,9 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -3553,12 +3664,12 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>26</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -3566,9 +3677,9 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B12" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="25">
         <v>1</v>
@@ -3579,9 +3690,9 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B13" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="33">
         <f>C12*60</f>
@@ -3593,9 +3704,9 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B14" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="25">
         <v>9750.4755283144204</v>
@@ -3606,9 +3717,9 @@
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B15" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="25">
         <v>82.232498168945298</v>
@@ -3619,9 +3730,9 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B16" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="20">
         <f>IF(C15&lt;$E$4,$F$4,IF(C15&lt;$E$5,$F$5,$F$6))</f>
@@ -3633,33 +3744,33 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B17" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="11">
         <f>IF(C15&lt;$E$4,(C14/$F$4)/3600,IF(C15&lt;$E$5,(C14/$F$5)/3600,(C14/$F$6)/3600))</f>
         <v>4.5141090408863063</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B18" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="11">
         <f>IF(C15&lt;$E$4,$G$4,IF(C15&lt;$E$5,$G$5,$G$6))</f>
         <v>0.1</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B19" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="30">
         <f>ROUND(IF(C15&lt;$E$4,$H$4,IF(C15&lt;$E$5,C14/(4*$F$5*C13),C14/($F$6*C13))),0)</f>
@@ -3667,70 +3778,70 @@
       </c>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B20" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="12">
         <f>IF(C19&gt;99,99,IF(C19=0,1,C19))</f>
         <v>68</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B22" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B23" s="39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="E23" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="F23" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="G23" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="H23" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="I23" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B24" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>57</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="K23" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="M23" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N23" s="41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B24" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>58</v>
       </c>
       <c r="D24" s="35">
         <v>1052.6874419186299</v>
@@ -3745,7 +3856,7 @@
         <v>3.7614733529000002E-5</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I24" s="35">
         <v>82.146202087402301</v>
@@ -3771,12 +3882,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B25" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D25" s="35">
         <v>2214.3688792489802</v>
@@ -3791,7 +3902,7 @@
         <v>2.2647843822209998E-3</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I25" s="35">
         <v>83.661056518554702</v>
@@ -3817,12 +3928,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B26" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" s="35">
         <v>812.52503404213098</v>
@@ -3837,7 +3948,7 @@
         <v>5.1934622792380002E-3</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I26" s="35">
         <v>84.264968872070298</v>
@@ -3863,12 +3974,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B27" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" s="35">
         <v>306.792701376602</v>
@@ -3883,7 +3994,7 @@
         <v>5.6461846849050002E-3</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I27" s="35">
         <v>81.087654113769503</v>
@@ -3909,12 +4020,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B28" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="35">
         <v>3138.1446037980099</v>
@@ -3929,7 +4040,7 @@
         <v>3.343825581022E-3</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I28" s="35">
         <v>83.017272949218807</v>
@@ -3955,12 +4066,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B29" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D29" s="35">
         <v>1504.4308351914499</v>
@@ -3975,7 +4086,7 @@
         <v>7.7746318411100004E-4</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I29" s="35">
         <v>90.837333679199205</v>
@@ -4001,12 +4112,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B30" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30" s="35">
         <v>480.31346950722002</v>
@@ -4021,7 +4132,7 @@
         <v>1.6366141051151001E-2</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I30" s="35">
         <v>98.604133605957003</v>
@@ -4047,12 +4158,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B31" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D31" s="35">
         <v>2007.8383952873301</v>
@@ -4067,7 +4178,7 @@
         <v>1.5727393220000002E-5</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I31" s="35">
         <v>98.528877258300795</v>
@@ -4093,12 +4204,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B32" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D32" s="35">
         <v>4419.1284818909598</v>
@@ -4113,7 +4224,7 @@
         <v>1.3624228080760001E-3</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I32" s="35">
         <v>106.842567443848</v>
@@ -4139,12 +4250,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B33" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D33" s="35">
         <v>9750.4755283144204</v>
@@ -4159,7 +4270,7 @@
         <v>1.371805433614E-3</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33" s="35">
         <v>82.232498168945298</v>
@@ -4185,12 +4296,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B34" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D34" s="35">
         <v>1948.7592425986099</v>
@@ -4205,7 +4316,7 @@
         <v>3.0023595150159999E-3</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I34" s="35">
         <v>78.631752014160199</v>
@@ -4231,12 +4342,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B35" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D35" s="35">
         <v>6791.2766201920904</v>
@@ -4251,7 +4362,7 @@
         <v>2.6934575189140001E-3</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I35" s="35">
         <v>87.634117126464801</v>
@@ -4277,12 +4388,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B36" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D36" s="35">
         <v>4676.4115953257196</v>
@@ -4297,7 +4408,7 @@
         <v>7.7427639541920003E-3</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I36" s="35">
         <v>109.323036193848</v>
@@ -4323,12 +4434,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B37" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D37" s="35">
         <v>2346.7349482674599</v>
@@ -4343,7 +4454,7 @@
         <v>6.5964881811700002E-3</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I37" s="35">
         <v>136.53871154785199</v>
@@ -4369,12 +4480,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B38" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="35">
         <v>4554.9148638168299</v>
@@ -4389,7 +4500,7 @@
         <v>6.4329577133910004E-3</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I38" s="35">
         <v>109.91001129150401</v>
@@ -4415,12 +4526,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B39" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" s="35">
         <v>8468.1780681584405</v>
@@ -4435,7 +4546,7 @@
         <v>9.0357547626199999E-4</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I39" s="35">
         <v>62.740562438964801</v>
@@ -4461,12 +4572,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B40" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D40" s="35">
         <v>5567.3194321154397</v>
@@ -4481,7 +4592,7 @@
         <v>1.5483753713219999E-3</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I40" s="35">
         <v>69.165557861328097</v>
@@ -4507,12 +4618,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B41" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D41" s="35">
         <v>1544.7590937973901</v>
@@ -4527,7 +4638,7 @@
         <v>1.3973847121969999E-3</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I41" s="35">
         <v>73.386154174804702</v>
@@ -4553,12 +4664,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B42" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D42" s="35">
         <v>3047.0183307345601</v>
@@ -4573,7 +4684,7 @@
         <v>6.0354232137399999E-4</v>
       </c>
       <c r="H42" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I42" s="35">
         <v>78.397857666015597</v>
@@ -4599,7 +4710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B43" s="37"/>
       <c r="C43" s="38"/>
       <c r="D43" s="38"/>
@@ -4626,44 +4737,1281 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD1961B-321B-4490-9B9C-D513C3F35BFB}">
+  <dimension ref="B1:N43"/>
+  <sheetFormatPr defaultColWidth="11.41015625" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="2.703125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="15.64453125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18.703125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="17.05859375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="10.64453125" style="10" customWidth="1"/>
+    <col min="6" max="7" width="10.64453125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12.64453125" style="9" customWidth="1"/>
+    <col min="9" max="14" width="10.64453125" style="9" customWidth="1"/>
+    <col min="15" max="16384" width="11.41015625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+    </row>
+    <row r="3" spans="2:8" ht="30" x14ac:dyDescent="0.5">
+      <c r="B3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B4" s="18">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="44">
+        <v>1E-3</v>
+      </c>
+      <c r="F4" s="44">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="44">
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B5" s="18">
+        <v>2</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="44">
+        <v>0.02</v>
+      </c>
+      <c r="F5" s="44">
+        <v>0.6</v>
+      </c>
+      <c r="G5" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B6" s="21">
+        <v>3</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="45">
+        <v>0.02</v>
+      </c>
+      <c r="F6" s="45">
+        <v>2</v>
+      </c>
+      <c r="G6" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B7" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B12" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="25">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B13" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="33">
+        <f>C12*60</f>
+        <v>60</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B14" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="25">
+        <v>9750.4755283144204</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B15" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="25">
+        <v>3.7614733529000002E-5</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.5">
+      <c r="B16" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="20">
+        <f>IF(C15&lt;$E$4,$F$4,IF(C15&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.25</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B17" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="11">
+        <f>IF(C15&lt;$E$4,(C14/$F$4)/3600,IF(C15&lt;$E$5,(C14/$F$5)/3600,(C14/$F$6)/3600))</f>
+        <v>10.833861698127134</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B18" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="11">
+        <f>IF(C15&lt;$E$4,$G$4,IF(C15&lt;$E$5,$G$5,$G$6))</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="30">
+        <f>ROUND(IF(C15&lt;$E$4,$H$4,IF(C15&lt;$E$5,C14/(4*$F$5*C13),C14/($F$6*C13))),0)</f>
+        <v>2</v>
+      </c>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B20" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="12">
+        <f>IF(C19&gt;99,99,IF(C19=0,1,C19))</f>
+        <v>2</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B22" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B23" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B24" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="35">
+        <v>1052.6874419186299</v>
+      </c>
+      <c r="E24" s="35">
+        <v>3.9596557617188E-2</v>
+      </c>
+      <c r="F24" s="35">
+        <v>1.09776265346198</v>
+      </c>
+      <c r="G24" s="42">
+        <v>3.7614733529000002E-5</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="35">
+        <v>82.146202087402301</v>
+      </c>
+      <c r="J24" s="34">
+        <f>IF(G24&lt;$E$4,$F$4,IF(I24&lt;$E$5,$F$5,$F$6))</f>
+        <v>0.25</v>
+      </c>
+      <c r="K24" s="34">
+        <f>ROUND(IF(G24&lt;$E$4,$H$4,IF(G24&lt;$E$5,D24/(4*$F$5*$C$13),D24/($F$6*$C$13))),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L24" s="34">
+        <f>IF(G24&lt;$E$4,(D24/$F$4)/3600,IF(G24&lt;$E$5,(D24/$F$5)/3600,(D24/$F$6)/3600))</f>
+        <v>1.1696527132429222</v>
+      </c>
+      <c r="M24" s="34">
+        <f>IF(G24&lt;$E$4,$G$4,IF(G24&lt;$E$5,$G$5,$G$6))</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="11">
+        <f>IF(K24&gt;99,99,IF(K24=0,1,K24))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B25" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="35">
+        <v>2214.3688792489802</v>
+      </c>
+      <c r="E25" s="35">
+        <v>5.0150680541992196</v>
+      </c>
+      <c r="F25" s="35">
+        <v>1.15260976611237</v>
+      </c>
+      <c r="G25" s="35">
+        <v>2.2647843822209998E-3</v>
+      </c>
+      <c r="H25" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="35">
+        <v>83.661056518554702</v>
+      </c>
+      <c r="J25" s="34">
+        <f t="shared" ref="J25:J42" si="0">IF(G25&lt;$E$4,$F$4,IF(I25&lt;$E$5,$F$5,$F$6))</f>
+        <v>2</v>
+      </c>
+      <c r="K25" s="34">
+        <f t="shared" ref="K25:K42" si="1">ROUND(IF(G25&lt;$E$4,$H$4,IF(G25&lt;$E$5,D25/(4*$F$5*$C$13),D25/($F$6*$C$13))),0)</f>
+        <v>15</v>
+      </c>
+      <c r="L25" s="34">
+        <f t="shared" ref="L25:L42" si="2">IF(G25&lt;$E$4,(D25/$F$4)/3600,IF(G25&lt;$E$5,(D25/$F$5)/3600,(D25/$F$6)/3600))</f>
+        <v>1.0251707774300836</v>
+      </c>
+      <c r="M25" s="34">
+        <f>IF(G25&lt;$E$4,$G$4,IF(G25&lt;$E$5,$G$5,$G$6))</f>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="11">
+        <f>IF(K25&gt;99,99,IF(K25=0,1,K25))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B26" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="35">
+        <v>812.52503404213098</v>
+      </c>
+      <c r="E26" s="35">
+        <v>4.2198181152343697</v>
+      </c>
+      <c r="F26" s="35">
+        <v>1.09971027809434</v>
+      </c>
+      <c r="G26" s="35">
+        <v>5.1934622792380002E-3</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="35">
+        <v>84.264968872070298</v>
+      </c>
+      <c r="J26" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K26" s="34">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L26" s="34">
+        <f t="shared" si="2"/>
+        <v>0.37616899724172737</v>
+      </c>
+      <c r="M26" s="34">
+        <f>IF(G26&lt;$E$4,$G$4,IF(G26&lt;$E$5,$G$5,$G$6))</f>
+        <v>0.1</v>
+      </c>
+      <c r="N26" s="11">
+        <f>IF(K26&gt;99,99,IF(K26=0,1,K26))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B27" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="35">
+        <v>306.792701376602</v>
+      </c>
+      <c r="E27" s="35">
+        <v>1.7322082519531199</v>
+      </c>
+      <c r="F27" s="35">
+        <v>1</v>
+      </c>
+      <c r="G27" s="35">
+        <v>5.6461846849050002E-3</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="35">
+        <v>81.087654113769503</v>
+      </c>
+      <c r="J27" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K27" s="34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L27" s="34">
+        <f t="shared" si="2"/>
+        <v>0.14203365804472315</v>
+      </c>
+      <c r="M27" s="34">
+        <f>IF(G27&lt;$E$4,$G$4,IF(G27&lt;$E$5,$G$5,$G$6))</f>
+        <v>0.1</v>
+      </c>
+      <c r="N27" s="11">
+        <f>IF(K27&gt;99,99,IF(K27=0,1,K27))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B28" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="35">
+        <v>3138.1446037980099</v>
+      </c>
+      <c r="E28" s="35">
+        <v>10.493408203125</v>
+      </c>
+      <c r="F28" s="35">
+        <v>1.1900200162855299</v>
+      </c>
+      <c r="G28" s="35">
+        <v>3.343825581022E-3</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="35">
+        <v>83.017272949218807</v>
+      </c>
+      <c r="J28" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K28" s="34">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="L28" s="34">
+        <f t="shared" si="2"/>
+        <v>1.4528447239805602</v>
+      </c>
+      <c r="M28" s="34">
+        <f>IF(G28&lt;$E$4,$G$4,IF(G28&lt;$E$5,$G$5,$G$6))</f>
+        <v>0.1</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" ref="N25:N42" si="3">IF(K28&gt;99,99,IF(K28=0,1,K28))</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B29" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="35">
+        <v>1504.4308351914499</v>
+      </c>
+      <c r="E29" s="35">
+        <v>1.16963958740234</v>
+      </c>
+      <c r="F29" s="35">
+        <v>1.2120932311380499</v>
+      </c>
+      <c r="G29" s="35">
+        <v>7.7746318411100004E-4</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" s="35">
+        <v>90.837333679199205</v>
+      </c>
+      <c r="J29" s="34">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="K29" s="34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L29" s="34">
+        <f t="shared" si="2"/>
+        <v>1.6715898168793888</v>
+      </c>
+      <c r="M29" s="34">
+        <f t="shared" ref="M25:M42" si="4">IF(G29&lt;$E$4,$G$4,IF(G29&lt;$E$5,$G$5,$G$6))</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B30" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="35">
+        <v>480.31346950722002</v>
+      </c>
+      <c r="E30" s="35">
+        <v>7.86087799072265</v>
+      </c>
+      <c r="F30" s="35">
+        <v>1.16696962122673</v>
+      </c>
+      <c r="G30" s="35">
+        <v>1.6366141051151001E-2</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="35">
+        <v>98.604133605957003</v>
+      </c>
+      <c r="J30" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K30" s="34">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L30" s="34">
+        <f t="shared" si="2"/>
+        <v>0.22236734699408336</v>
+      </c>
+      <c r="M30" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N30" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B31" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="35">
+        <v>2007.8383952873301</v>
+      </c>
+      <c r="E31" s="35">
+        <v>3.1578063964844E-2</v>
+      </c>
+      <c r="F31" s="35">
+        <v>1.0778579614880499</v>
+      </c>
+      <c r="G31" s="42">
+        <v>1.5727393220000002E-5</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" s="35">
+        <v>98.528877258300795</v>
+      </c>
+      <c r="J31" s="34">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="K31" s="34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L31" s="34">
+        <f t="shared" si="2"/>
+        <v>2.2309315503192555</v>
+      </c>
+      <c r="M31" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B32" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="35">
+        <v>4419.1284818909598</v>
+      </c>
+      <c r="E32" s="35">
+        <v>6.0207214355468697</v>
+      </c>
+      <c r="F32" s="35">
+        <v>1.22495673931062</v>
+      </c>
+      <c r="G32" s="35">
+        <v>1.3624228080760001E-3</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="35">
+        <v>106.842567443848</v>
+      </c>
+      <c r="J32" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K32" s="34">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="L32" s="34">
+        <f t="shared" si="2"/>
+        <v>2.0458928156902592</v>
+      </c>
+      <c r="M32" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N32" s="11">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B33" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="35">
+        <v>9750.4755283144204</v>
+      </c>
+      <c r="E33" s="35">
+        <v>13.3757553100585</v>
+      </c>
+      <c r="F33" s="35">
+        <v>1.2673326759994901</v>
+      </c>
+      <c r="G33" s="35">
+        <v>1.371805433614E-3</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="35">
+        <v>82.232498168945298</v>
+      </c>
+      <c r="J33" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K33" s="34">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="L33" s="34">
+        <f t="shared" si="2"/>
+        <v>4.5141090408863063</v>
+      </c>
+      <c r="M33" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N33" s="11">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B34" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="35">
+        <v>1948.7592425986099</v>
+      </c>
+      <c r="E34" s="35">
+        <v>5.8508758544921804</v>
+      </c>
+      <c r="F34" s="35">
+        <v>1.46329755411188</v>
+      </c>
+      <c r="G34" s="35">
+        <v>3.0023595150159999E-3</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="35">
+        <v>78.631752014160199</v>
+      </c>
+      <c r="J34" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K34" s="34">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="L34" s="34">
+        <f t="shared" si="2"/>
+        <v>0.90220335305491206</v>
+      </c>
+      <c r="M34" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N34" s="11">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B35" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="35">
+        <v>6791.2766201920904</v>
+      </c>
+      <c r="E35" s="35">
+        <v>18.292015075683501</v>
+      </c>
+      <c r="F35" s="35">
+        <v>1.1682867633829599</v>
+      </c>
+      <c r="G35" s="35">
+        <v>2.6934575189140001E-3</v>
+      </c>
+      <c r="H35" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I35" s="35">
+        <v>87.634117126464801</v>
+      </c>
+      <c r="J35" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K35" s="34">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="L35" s="34">
+        <f t="shared" si="2"/>
+        <v>3.1441095463852271</v>
+      </c>
+      <c r="M35" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N35" s="11">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B36" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="35">
+        <v>4676.4115953257196</v>
+      </c>
+      <c r="E36" s="35">
+        <v>36.208351135253899</v>
+      </c>
+      <c r="F36" s="35">
+        <v>1.2637308364015001</v>
+      </c>
+      <c r="G36" s="35">
+        <v>7.7427639541920003E-3</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I36" s="35">
+        <v>109.323036193848</v>
+      </c>
+      <c r="J36" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K36" s="34">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="L36" s="34">
+        <f t="shared" si="2"/>
+        <v>2.1650053682063519</v>
+      </c>
+      <c r="M36" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N36" s="11">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B37" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="35">
+        <v>2346.7349482674599</v>
+      </c>
+      <c r="E37" s="35">
+        <v>15.4802093505859</v>
+      </c>
+      <c r="F37" s="35">
+        <v>1.2662899618863199</v>
+      </c>
+      <c r="G37" s="35">
+        <v>6.5964881811700002E-3</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="35">
+        <v>136.53871154785199</v>
+      </c>
+      <c r="J37" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K37" s="34">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L37" s="34">
+        <f t="shared" si="2"/>
+        <v>1.0864513649386389</v>
+      </c>
+      <c r="M37" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N37" s="11">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B38" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="35">
+        <v>4554.9148638168299</v>
+      </c>
+      <c r="E38" s="35">
+        <v>29.3015747070312</v>
+      </c>
+      <c r="F38" s="35">
+        <v>1.5905670202208699</v>
+      </c>
+      <c r="G38" s="35">
+        <v>6.4329577133910004E-3</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" s="35">
+        <v>109.91001129150401</v>
+      </c>
+      <c r="J38" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="34">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="L38" s="34">
+        <f t="shared" si="2"/>
+        <v>2.1087568813966806</v>
+      </c>
+      <c r="M38" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N38" s="11">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B39" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="35">
+        <v>8468.1780681584405</v>
+      </c>
+      <c r="E39" s="35">
+        <v>7.6516380310058603</v>
+      </c>
+      <c r="F39" s="35">
+        <v>1.21591229968776</v>
+      </c>
+      <c r="G39" s="35">
+        <v>9.0357547626199999E-4</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I39" s="35">
+        <v>62.740562438964801</v>
+      </c>
+      <c r="J39" s="34">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="K39" s="34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L39" s="34">
+        <f t="shared" si="2"/>
+        <v>9.4090867423982676</v>
+      </c>
+      <c r="M39" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B40" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="35">
+        <v>5567.3194321154397</v>
+      </c>
+      <c r="E40" s="35">
+        <v>8.62030029296875</v>
+      </c>
+      <c r="F40" s="35">
+        <v>1.2950148610724099</v>
+      </c>
+      <c r="G40" s="35">
+        <v>1.5483753713219999E-3</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" s="35">
+        <v>69.165557861328097</v>
+      </c>
+      <c r="J40" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K40" s="34">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="L40" s="34">
+        <f t="shared" si="2"/>
+        <v>2.5774627000534442</v>
+      </c>
+      <c r="M40" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N40" s="11">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B41" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="35">
+        <v>1544.7590937973901</v>
+      </c>
+      <c r="E41" s="35">
+        <v>2.1586227416992099</v>
+      </c>
+      <c r="F41" s="35">
+        <v>1.2910739843402099</v>
+      </c>
+      <c r="G41" s="35">
+        <v>1.3973847121969999E-3</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I41" s="35">
+        <v>73.386154174804702</v>
+      </c>
+      <c r="J41" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K41" s="34">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L41" s="34">
+        <f t="shared" si="2"/>
+        <v>0.71516624712842136</v>
+      </c>
+      <c r="M41" s="34">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="N41" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B42" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="35">
+        <v>3047.0183307345601</v>
+      </c>
+      <c r="E42" s="35">
+        <v>1.8390045166015601</v>
+      </c>
+      <c r="F42" s="35">
+        <v>1.4072559008632799</v>
+      </c>
+      <c r="G42" s="35">
+        <v>6.0354232137399999E-4</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="35">
+        <v>78.397857666015597</v>
+      </c>
+      <c r="J42" s="34">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="K42" s="34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L42" s="34">
+        <f t="shared" si="2"/>
+        <v>3.3855759230384002</v>
+      </c>
+      <c r="M42" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.5">
+      <c r="B43" s="37"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B7:H8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA9BBA55-1A16-4669-AEC1-4C38582E7DEA}">
   <dimension ref="B2:B22"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.41015625" defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="63.86328125" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="11.3984375" style="2"/>
+    <col min="1" max="1" width="2.703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="63.87890625" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="11.41015625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.5">
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>

--- a/file/table/TSIG_Muskingum.xlsx
+++ b/file/table/TSIG_Muskingum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6851D60-31AE-4AFA-8029-7B0C3AA300B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE26F0A-4519-43AF-827F-E3D66A3F2CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" activeTab="3" xr2:uid="{293BEA77-BE37-42CC-81CC-CF669E9BF0C2}"/>
   </bookViews>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
   <si>
     <t>≥ 300</t>
   </si>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t>Password: 1234</t>
-  </si>
-  <si>
-    <t>Nota: Aplica solo para este caso de estudio, correspondiente a las cuencas hidrográficas del Departamento del Cesar en Colombia - Suramérica. Cada zona geográfica debe ser evaluada en función del rango de elevaciones del terreno.</t>
   </si>
   <si>
     <t>Factor de ponderación X</t>
@@ -505,6 +502,12 @@
   </si>
   <si>
     <t>Parámetros Muskingum a partir de la reclasificación de zonas topográficas</t>
+  </si>
+  <si>
+    <t>Nota: los rangos y valores aplican a las cuencas hidrográficas del Departamento del Cesar en Colombia - Suramérica. Cada zona geográfica debe ser evaluada en función del rango de elevaciones del terreno.</t>
+  </si>
+  <si>
+    <t>Nota: los rangos y valores aplican a las cuencas hidrográficas del Departamento del Cesar en Colombia - Suramérica. Cada zona geográfica debe ser evaluada en función del rango de pendientes de cauces.</t>
   </si>
 </sst>
 </file>
@@ -1807,12 +1810,12 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B4" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.65">
@@ -1820,7 +1823,7 @@
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B6" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="47.25" customHeight="1" x14ac:dyDescent="0.65">
@@ -1828,7 +1831,7 @@
     </row>
     <row r="8" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
       <c r="B8" s="32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="48" customHeight="1" x14ac:dyDescent="0.65">
@@ -1836,7 +1839,7 @@
     </row>
     <row r="10" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
       <c r="B10" s="32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="159" customHeight="1" x14ac:dyDescent="0.65">
@@ -1844,7 +1847,7 @@
     </row>
     <row r="12" spans="2:2" ht="49" x14ac:dyDescent="0.65">
       <c r="B12" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.65">
@@ -1852,12 +1855,12 @@
     </row>
     <row r="14" spans="2:2" ht="49" x14ac:dyDescent="0.65">
       <c r="B14" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B15" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="39" customHeight="1" x14ac:dyDescent="0.65">
@@ -1865,7 +1868,7 @@
     </row>
     <row r="17" spans="2:2" ht="81.7" x14ac:dyDescent="0.65">
       <c r="B17" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="138.75" customHeight="1" x14ac:dyDescent="0.65">
@@ -1873,12 +1876,12 @@
     </row>
     <row r="19" spans="2:2" ht="49" x14ac:dyDescent="0.65">
       <c r="B19" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
       <c r="B20" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.65">
@@ -1886,7 +1889,7 @@
     </row>
     <row r="22" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
       <c r="B22" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.65">
@@ -2665,12 +2668,12 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="81.7" x14ac:dyDescent="0.65">
       <c r="B4" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.65">
@@ -2678,7 +2681,7 @@
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.65">
       <c r="B6" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.65">
@@ -2686,7 +2689,7 @@
     </row>
     <row r="8" spans="2:2" ht="326.7" x14ac:dyDescent="0.65">
       <c r="B8" s="32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.65">
@@ -2694,7 +2697,7 @@
     </row>
     <row r="10" spans="2:2" ht="32.700000000000003" x14ac:dyDescent="0.65">
       <c r="B10" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.65">
@@ -3523,7 +3526,7 @@
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" s="46"/>
       <c r="D2" s="46"/>
@@ -3532,7 +3535,7 @@
       <c r="G2" s="46"/>
       <c r="H2" s="46"/>
     </row>
-    <row r="3" spans="2:8" ht="30" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:8" ht="45" x14ac:dyDescent="0.5">
       <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
@@ -3540,19 +3543,19 @@
         <v>6</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>15</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.5">
@@ -3598,7 +3601,7 @@
         <v>0.1</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.5">
@@ -3621,12 +3624,12 @@
         <v>0.2</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B7" s="46" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C7" s="46"/>
       <c r="D7" s="46"/>
@@ -3655,7 +3658,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -3666,10 +3669,10 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B11" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -3679,7 +3682,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B12" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="25">
         <v>1</v>
@@ -3692,7 +3695,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B13" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="33">
         <f>C12*60</f>
@@ -3706,7 +3709,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B14" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="25">
         <v>9750.4755283144204</v>
@@ -3719,7 +3722,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B15" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="25">
         <v>82.232498168945298</v>
@@ -3732,7 +3735,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B16" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="20">
         <f>IF(C15&lt;$E$4,$F$4,IF(C15&lt;$E$5,$F$5,$F$6))</f>
@@ -3746,31 +3749,31 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B17" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="11">
         <f>IF(C15&lt;$E$4,(C14/$F$4)/3600,IF(C15&lt;$E$5,(C14/$F$5)/3600,(C14/$F$6)/3600))</f>
         <v>4.5141090408863063</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B18" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="11">
         <f>IF(C15&lt;$E$4,$G$4,IF(C15&lt;$E$5,$G$5,$G$6))</f>
         <v>0.1</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B19" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="30">
         <f>ROUND(IF(C15&lt;$E$4,$H$4,IF(C15&lt;$E$5,C14/(4*$F$5*C13),C14/($F$6*C13))),0)</f>
@@ -3780,68 +3783,68 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B20" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="12">
         <f>IF(C19&gt;99,99,IF(C19=0,1,C19))</f>
         <v>68</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B22" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B23" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="E23" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="F23" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="G23" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="H23" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="40" t="s">
-        <v>56</v>
-      </c>
       <c r="I23" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="J23" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="K23" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="40" t="s">
+      <c r="M23" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="41" t="s">
         <v>79</v>
-      </c>
-      <c r="M23" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="41" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B24" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="35">
         <v>1052.6874419186299</v>
@@ -3856,7 +3859,7 @@
         <v>3.7614733529000002E-5</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I24" s="35">
         <v>82.146202087402301</v>
@@ -3884,10 +3887,10 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B25" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="35">
         <v>2214.3688792489802</v>
@@ -3902,7 +3905,7 @@
         <v>2.2647843822209998E-3</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I25" s="35">
         <v>83.661056518554702</v>
@@ -3930,10 +3933,10 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B26" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="35">
         <v>812.52503404213098</v>
@@ -3948,7 +3951,7 @@
         <v>5.1934622792380002E-3</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I26" s="35">
         <v>84.264968872070298</v>
@@ -3976,10 +3979,10 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B27" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="35">
         <v>306.792701376602</v>
@@ -3994,7 +3997,7 @@
         <v>5.6461846849050002E-3</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I27" s="35">
         <v>81.087654113769503</v>
@@ -4022,10 +4025,10 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B28" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="35">
         <v>3138.1446037980099</v>
@@ -4040,7 +4043,7 @@
         <v>3.343825581022E-3</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I28" s="35">
         <v>83.017272949218807</v>
@@ -4068,10 +4071,10 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B29" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="35">
         <v>1504.4308351914499</v>
@@ -4086,7 +4089,7 @@
         <v>7.7746318411100004E-4</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I29" s="35">
         <v>90.837333679199205</v>
@@ -4114,10 +4117,10 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B30" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" s="35">
         <v>480.31346950722002</v>
@@ -4132,7 +4135,7 @@
         <v>1.6366141051151001E-2</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I30" s="35">
         <v>98.604133605957003</v>
@@ -4160,10 +4163,10 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B31" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="35">
         <v>2007.8383952873301</v>
@@ -4178,7 +4181,7 @@
         <v>1.5727393220000002E-5</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I31" s="35">
         <v>98.528877258300795</v>
@@ -4206,10 +4209,10 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B32" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D32" s="35">
         <v>4419.1284818909598</v>
@@ -4224,7 +4227,7 @@
         <v>1.3624228080760001E-3</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I32" s="35">
         <v>106.842567443848</v>
@@ -4252,10 +4255,10 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B33" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" s="35">
         <v>9750.4755283144204</v>
@@ -4270,7 +4273,7 @@
         <v>1.371805433614E-3</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I33" s="35">
         <v>82.232498168945298</v>
@@ -4298,10 +4301,10 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D34" s="35">
         <v>1948.7592425986099</v>
@@ -4316,7 +4319,7 @@
         <v>3.0023595150159999E-3</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I34" s="35">
         <v>78.631752014160199</v>
@@ -4344,10 +4347,10 @@
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B35" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" s="35">
         <v>6791.2766201920904</v>
@@ -4362,7 +4365,7 @@
         <v>2.6934575189140001E-3</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I35" s="35">
         <v>87.634117126464801</v>
@@ -4390,10 +4393,10 @@
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B36" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D36" s="35">
         <v>4676.4115953257196</v>
@@ -4408,7 +4411,7 @@
         <v>7.7427639541920003E-3</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I36" s="35">
         <v>109.323036193848</v>
@@ -4436,10 +4439,10 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B37" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" s="35">
         <v>2346.7349482674599</v>
@@ -4454,7 +4457,7 @@
         <v>6.5964881811700002E-3</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I37" s="35">
         <v>136.53871154785199</v>
@@ -4482,10 +4485,10 @@
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B38" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D38" s="35">
         <v>4554.9148638168299</v>
@@ -4500,7 +4503,7 @@
         <v>6.4329577133910004E-3</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I38" s="35">
         <v>109.91001129150401</v>
@@ -4528,10 +4531,10 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B39" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D39" s="35">
         <v>8468.1780681584405</v>
@@ -4546,7 +4549,7 @@
         <v>9.0357547626199999E-4</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I39" s="35">
         <v>62.740562438964801</v>
@@ -4574,10 +4577,10 @@
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B40" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="35">
         <v>5567.3194321154397</v>
@@ -4592,7 +4595,7 @@
         <v>1.5483753713219999E-3</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I40" s="35">
         <v>69.165557861328097</v>
@@ -4620,10 +4623,10 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B41" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" s="35">
         <v>1544.7590937973901</v>
@@ -4638,7 +4641,7 @@
         <v>1.3973847121969999E-3</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I41" s="35">
         <v>73.386154174804702</v>
@@ -4666,10 +4669,10 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B42" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D42" s="35">
         <v>3047.0183307345601</v>
@@ -4684,7 +4687,7 @@
         <v>6.0354232137399999E-4</v>
       </c>
       <c r="H42" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I42" s="35">
         <v>78.397857666015597</v>
@@ -4760,7 +4763,7 @@
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="46"/>
       <c r="D2" s="46"/>
@@ -4769,7 +4772,7 @@
       <c r="G2" s="46"/>
       <c r="H2" s="46"/>
     </row>
-    <row r="3" spans="2:8" ht="30" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:8" ht="45" x14ac:dyDescent="0.5">
       <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
@@ -4777,19 +4780,19 @@
         <v>6</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>15</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.5">
@@ -4800,7 +4803,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" s="44">
         <v>1E-3</v>
@@ -4823,7 +4826,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" s="44">
         <v>0.02</v>
@@ -4835,7 +4838,7 @@
         <v>0.1</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.5">
@@ -4846,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" s="45">
         <v>0.02</v>
@@ -4858,12 +4861,12 @@
         <v>0.2</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B7" s="46" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C7" s="46"/>
       <c r="D7" s="46"/>
@@ -4892,7 +4895,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -4903,10 +4906,10 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B11" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -4916,7 +4919,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B12" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="25">
         <v>1</v>
@@ -4929,7 +4932,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B13" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="33">
         <f>C12*60</f>
@@ -4943,7 +4946,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B14" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="25">
         <v>9750.4755283144204</v>
@@ -4956,7 +4959,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B15" s="26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="25">
         <v>3.7614733529000002E-5</v>
@@ -4969,7 +4972,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.5">
       <c r="B16" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="20">
         <f>IF(C15&lt;$E$4,$F$4,IF(C15&lt;$E$5,$F$5,$F$6))</f>
@@ -4983,31 +4986,31 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B17" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="11">
         <f>IF(C15&lt;$E$4,(C14/$F$4)/3600,IF(C15&lt;$E$5,(C14/$F$5)/3600,(C14/$F$6)/3600))</f>
         <v>10.833861698127134</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B18" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="11">
         <f>IF(C15&lt;$E$4,$G$4,IF(C15&lt;$E$5,$G$5,$G$6))</f>
         <v>0</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B19" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="30">
         <f>ROUND(IF(C15&lt;$E$4,$H$4,IF(C15&lt;$E$5,C14/(4*$F$5*C13),C14/($F$6*C13))),0)</f>
@@ -5017,68 +5020,68 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B20" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="12">
         <f>IF(C19&gt;99,99,IF(C19=0,1,C19))</f>
         <v>2</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B22" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B23" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="E23" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="F23" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="G23" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="H23" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="40" t="s">
-        <v>56</v>
-      </c>
       <c r="I23" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="J23" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="K23" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="40" t="s">
+      <c r="M23" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="41" t="s">
         <v>79</v>
-      </c>
-      <c r="M23" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="41" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B24" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="35">
         <v>1052.6874419186299</v>
@@ -5093,7 +5096,7 @@
         <v>3.7614733529000002E-5</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I24" s="35">
         <v>82.146202087402301</v>
@@ -5121,10 +5124,10 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B25" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="35">
         <v>2214.3688792489802</v>
@@ -5139,7 +5142,7 @@
         <v>2.2647843822209998E-3</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I25" s="35">
         <v>83.661056518554702</v>
@@ -5167,10 +5170,10 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B26" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="35">
         <v>812.52503404213098</v>
@@ -5185,7 +5188,7 @@
         <v>5.1934622792380002E-3</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I26" s="35">
         <v>84.264968872070298</v>
@@ -5213,10 +5216,10 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B27" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="35">
         <v>306.792701376602</v>
@@ -5231,7 +5234,7 @@
         <v>5.6461846849050002E-3</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I27" s="35">
         <v>81.087654113769503</v>
@@ -5259,10 +5262,10 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B28" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="35">
         <v>3138.1446037980099</v>
@@ -5277,7 +5280,7 @@
         <v>3.343825581022E-3</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I28" s="35">
         <v>83.017272949218807</v>
@@ -5299,16 +5302,16 @@
         <v>0.1</v>
       </c>
       <c r="N28" s="11">
-        <f t="shared" ref="N25:N42" si="3">IF(K28&gt;99,99,IF(K28=0,1,K28))</f>
+        <f t="shared" ref="N28:N42" si="3">IF(K28&gt;99,99,IF(K28=0,1,K28))</f>
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B29" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="35">
         <v>1504.4308351914499</v>
@@ -5323,7 +5326,7 @@
         <v>7.7746318411100004E-4</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I29" s="35">
         <v>90.837333679199205</v>
@@ -5341,7 +5344,7 @@
         <v>1.6715898168793888</v>
       </c>
       <c r="M29" s="34">
-        <f t="shared" ref="M25:M42" si="4">IF(G29&lt;$E$4,$G$4,IF(G29&lt;$E$5,$G$5,$G$6))</f>
+        <f t="shared" ref="M29:M42" si="4">IF(G29&lt;$E$4,$G$4,IF(G29&lt;$E$5,$G$5,$G$6))</f>
         <v>0</v>
       </c>
       <c r="N29" s="11">
@@ -5351,10 +5354,10 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B30" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" s="35">
         <v>480.31346950722002</v>
@@ -5369,7 +5372,7 @@
         <v>1.6366141051151001E-2</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I30" s="35">
         <v>98.604133605957003</v>
@@ -5397,10 +5400,10 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B31" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="35">
         <v>2007.8383952873301</v>
@@ -5415,7 +5418,7 @@
         <v>1.5727393220000002E-5</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I31" s="35">
         <v>98.528877258300795</v>
@@ -5443,10 +5446,10 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B32" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D32" s="35">
         <v>4419.1284818909598</v>
@@ -5461,7 +5464,7 @@
         <v>1.3624228080760001E-3</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I32" s="35">
         <v>106.842567443848</v>
@@ -5489,10 +5492,10 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B33" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" s="35">
         <v>9750.4755283144204</v>
@@ -5507,7 +5510,7 @@
         <v>1.371805433614E-3</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I33" s="35">
         <v>82.232498168945298</v>
@@ -5535,10 +5538,10 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D34" s="35">
         <v>1948.7592425986099</v>
@@ -5553,7 +5556,7 @@
         <v>3.0023595150159999E-3</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I34" s="35">
         <v>78.631752014160199</v>
@@ -5581,10 +5584,10 @@
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B35" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" s="35">
         <v>6791.2766201920904</v>
@@ -5599,7 +5602,7 @@
         <v>2.6934575189140001E-3</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I35" s="35">
         <v>87.634117126464801</v>
@@ -5627,10 +5630,10 @@
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B36" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D36" s="35">
         <v>4676.4115953257196</v>
@@ -5645,7 +5648,7 @@
         <v>7.7427639541920003E-3</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I36" s="35">
         <v>109.323036193848</v>
@@ -5673,10 +5676,10 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B37" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" s="35">
         <v>2346.7349482674599</v>
@@ -5691,7 +5694,7 @@
         <v>6.5964881811700002E-3</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I37" s="35">
         <v>136.53871154785199</v>
@@ -5719,10 +5722,10 @@
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B38" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D38" s="35">
         <v>4554.9148638168299</v>
@@ -5737,7 +5740,7 @@
         <v>6.4329577133910004E-3</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I38" s="35">
         <v>109.91001129150401</v>
@@ -5765,10 +5768,10 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B39" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D39" s="35">
         <v>8468.1780681584405</v>
@@ -5783,7 +5786,7 @@
         <v>9.0357547626199999E-4</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I39" s="35">
         <v>62.740562438964801</v>
@@ -5811,10 +5814,10 @@
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B40" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="35">
         <v>5567.3194321154397</v>
@@ -5829,7 +5832,7 @@
         <v>1.5483753713219999E-3</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I40" s="35">
         <v>69.165557861328097</v>
@@ -5857,10 +5860,10 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B41" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" s="35">
         <v>1544.7590937973901</v>
@@ -5875,7 +5878,7 @@
         <v>1.3973847121969999E-3</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I41" s="35">
         <v>73.386154174804702</v>
@@ -5903,10 +5906,10 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.5">
       <c r="B42" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D42" s="35">
         <v>3047.0183307345601</v>
@@ -5921,7 +5924,7 @@
         <v>6.0354232137399999E-4</v>
       </c>
       <c r="H42" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I42" s="35">
         <v>78.397857666015597</v>
